--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[8, 8, 3, 6, 3]</t>
+          <t>[7, 1, 2, 7, 9]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,22 +472,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9459050515266583</v>
+        <v>0.9570717966998844</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9459050515266583</v>
+        <v>0.9570717966998844</v>
       </c>
       <c r="E2" t="n">
-        <v>96.41</v>
+        <v>99.10000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>71.84999999999999</v>
+        <v>75.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[8, 1, 5, 3, 0]</t>
+          <t>[0, 2, 8, 2, 8]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,22 +496,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9591780796947886</v>
+        <v>0.9648980383858681</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9591780796947886</v>
+        <v>0.9648980383858681</v>
       </c>
       <c r="E3" t="n">
-        <v>97.69</v>
+        <v>86.96000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>68.28</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[5, 5, 7, 7, 9]</t>
+          <t>[8, 1, 0, 2, 8]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,94 +520,94 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9452281521244915</v>
+        <v>0.9650316968973885</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9452281521244915</v>
+        <v>0.9650316968973885</v>
       </c>
       <c r="E4" t="n">
-        <v>95.44</v>
+        <v>92.66</v>
       </c>
       <c r="F4" t="n">
-        <v>68.17</v>
+        <v>77.44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[5, 2, 2, 1, 0]</t>
+          <t>[4, 7, 5, 4, 4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9806813659434201</v>
+        <v>0.9546196165581458</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9806813659434201</v>
+        <v>0.9546196165581458</v>
       </c>
       <c r="E5" t="n">
-        <v>99.56999999999999</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>77.52</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[2, 8, 3, 2, 2]</t>
+          <t>[0, 3, 4, 5, 3]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9760986165166281</v>
+        <v>0.9691606067341996</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9760986165166281</v>
+        <v>0.9691606067341996</v>
       </c>
       <c r="E6" t="n">
-        <v>98.22</v>
+        <v>81.88</v>
       </c>
       <c r="F6" t="n">
-        <v>76.58000000000001</v>
+        <v>72.83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[6, 0, 7, 8, 9]</t>
+          <t>[9, 3, 3, 5, 6]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9448724770500405</v>
+        <v>0.962043132865551</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9448724770500405</v>
+        <v>0.962043132865551</v>
       </c>
       <c r="E7" t="n">
-        <v>88.75999999999999</v>
+        <v>96.64</v>
       </c>
       <c r="F7" t="n">
-        <v>72.36</v>
+        <v>71.81999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[8, 1, 7, 4, 2]</t>
+          <t>[4, 6, 1, 6, 2]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -616,46 +616,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9519352054761016</v>
+        <v>0.9553018482827768</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9519352054761016</v>
+        <v>0.9553018482827768</v>
       </c>
       <c r="E8" t="n">
-        <v>90.66999999999999</v>
+        <v>90.46000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>68.36</v>
+        <v>74.78999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[6, 7, 2, 7, 9]</t>
+          <t>[6, 3, 8, 4, 5]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9439955181637396</v>
+        <v>0.9766190601830285</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9439955181637396</v>
+        <v>0.9766190601830285</v>
       </c>
       <c r="E9" t="n">
-        <v>86.13</v>
+        <v>96.36000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>65.72</v>
+        <v>75.60000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[2, 3, 1, 2, 4]</t>
+          <t>[8, 0, 6, 6, 6]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -664,94 +664,94 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9703250951923192</v>
+        <v>0.9509969520812122</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9703250951923192</v>
+        <v>0.9509969520812122</v>
       </c>
       <c r="E10" t="n">
-        <v>87.47999999999999</v>
+        <v>85.38</v>
       </c>
       <c r="F10" t="n">
-        <v>62.94</v>
+        <v>69.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[0, 5, 5, 9, 4]</t>
+          <t>[3, 8, 3, 6, 5]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9531853877942034</v>
+        <v>0.958128180595092</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9531853877942034</v>
+        <v>0.958128180595092</v>
       </c>
       <c r="E11" t="n">
-        <v>89.92999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="F11" t="n">
-        <v>75.7</v>
+        <v>68.25999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[7, 8, 5, 8, 0]</t>
+          <t>[3, 5, 4, 2, 6]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.941984371484285</v>
+        <v>0.979045312092373</v>
       </c>
       <c r="D12" t="n">
-        <v>0.941984371484285</v>
+        <v>0.979045312092373</v>
       </c>
       <c r="E12" t="n">
-        <v>94.28999999999999</v>
+        <v>91.38</v>
       </c>
       <c r="F12" t="n">
-        <v>76.63</v>
+        <v>77.12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[8, 3, 8, 8, 4]</t>
+          <t>[3, 5, 5, 6, 3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9446585210820503</v>
+        <v>0.9734705725199746</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9446585210820503</v>
+        <v>0.9734705725199746</v>
       </c>
       <c r="E13" t="n">
-        <v>96.63999999999999</v>
+        <v>89.91999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>77.53999999999999</v>
+        <v>64.72</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[5, 3, 6, 6, 0]</t>
+          <t>[1, 4, 2, 0, 6]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,46 +760,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9528804597996986</v>
+        <v>0.9692439808251494</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9528804597996986</v>
+        <v>0.9692439808251494</v>
       </c>
       <c r="E14" t="n">
-        <v>85.98999999999998</v>
+        <v>85.96000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>76.34</v>
+        <v>78.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[5, 4, 0, 2, 5]</t>
+          <t>[8, 3, 8, 3, 8]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9662525090999228</v>
+        <v>0.9658779296708239</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9662525090999228</v>
+        <v>0.9658779296708239</v>
       </c>
       <c r="E15" t="n">
-        <v>85.58999999999999</v>
+        <v>95.46000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>77.11</v>
+        <v>70.56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[8, 5, 8, 1, 8]</t>
+          <t>[2, 6, 1, 8, 9]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,46 +808,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9488414297624733</v>
+        <v>0.9544835383543275</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9488414297624733</v>
+        <v>0.9544835383543275</v>
       </c>
       <c r="E16" t="n">
-        <v>98.53</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>73.52</v>
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[6, 1, 9, 6, 5]</t>
+          <t>[3, 5, 0, 8, 5]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9430871171758416</v>
+        <v>0.9815692689145882</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9430871171758416</v>
+        <v>0.9815692689145882</v>
       </c>
       <c r="E17" t="n">
-        <v>87.25999999999999</v>
+        <v>96.18000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>69.45999999999999</v>
+        <v>75.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[1, 5, 4, 9, 9]</t>
+          <t>[6, 9, 6, 5, 7]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,22 +856,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9521205903499829</v>
+        <v>0.9441126096099557</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9521205903499829</v>
+        <v>0.9441126096099557</v>
       </c>
       <c r="E18" t="n">
-        <v>93.67999999999999</v>
+        <v>89.50999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>64.47</v>
+        <v>65.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[6, 6, 5, 4, 9]</t>
+          <t>[4, 1, 6, 0, 8]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -880,22 +880,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9485066785395706</v>
+        <v>0.9620855629054981</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9485066785395706</v>
+        <v>0.9620855629054981</v>
       </c>
       <c r="E19" t="n">
-        <v>82.89</v>
+        <v>86.34</v>
       </c>
       <c r="F19" t="n">
-        <v>77.83</v>
+        <v>74.04000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[9, 5, 7, 4, 3]</t>
+          <t>[1, 6, 8, 0, 6]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -904,46 +904,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9438698591316809</v>
+        <v>0.9591489032530607</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9438698591316809</v>
+        <v>0.9591489032530607</v>
       </c>
       <c r="E20" t="n">
-        <v>95.02999999999999</v>
+        <v>91.47999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>68.59999999999999</v>
+        <v>71.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[8, 1, 9, 6, 4]</t>
+          <t>[3, 0, 3, 3, 5]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9423954522862632</v>
+        <v>0.9858289534308138</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9423954522862632</v>
+        <v>0.9858289534308138</v>
       </c>
       <c r="E21" t="n">
-        <v>89.97</v>
+        <v>98.64</v>
       </c>
       <c r="F21" t="n">
-        <v>70.8</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[2, 1, 8, 3, 4]</t>
+          <t>[9, 4, 1, 3, 9]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,46 +952,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9631122899659681</v>
+        <v>0.9589646194726471</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9631122899659681</v>
+        <v>0.9589646194726471</v>
       </c>
       <c r="E22" t="n">
-        <v>92.72999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="F22" t="n">
-        <v>66.83</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[8, 8, 7, 5, 3]</t>
+          <t>[7, 3, 2, 5, 6]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9416514926169739</v>
+        <v>0.9756109033612697</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9416514926169739</v>
+        <v>0.9756109033612697</v>
       </c>
       <c r="E23" t="n">
-        <v>98.97</v>
+        <v>98.00999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>72.34999999999999</v>
+        <v>75.51000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[3, 8, 2, 7, 1]</t>
+          <t>[3, 2, 5, 5, 6]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1000,22 +1000,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9528580284537462</v>
+        <v>0.9635044104364154</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9528580284537462</v>
+        <v>0.9635044104364154</v>
       </c>
       <c r="E24" t="n">
-        <v>95.61999999999999</v>
+        <v>81.69999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>62.05</v>
+        <v>62.81</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[4, 9, 6, 6, 2]</t>
+          <t>[7, 8, 5, 8, 5]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9409520470028826</v>
+        <v>0.943255770381941</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9409520470028826</v>
+        <v>0.943255770381941</v>
       </c>
       <c r="E25" t="n">
-        <v>78.19999999999999</v>
+        <v>88.94999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>74.34999999999999</v>
+        <v>62.38</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[0, 7, 9, 0, 6]</t>
+          <t>[4, 5, 6, 3, 8]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9528165061373699</v>
+        <v>0.9567911819564763</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9528165061373699</v>
+        <v>0.9567911819564763</v>
       </c>
       <c r="E26" t="n">
-        <v>86</v>
+        <v>78.53999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>71.88</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[5, 1, 9, 9, 5]</t>
+          <t>[7, 8, 9, 0, 1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.945606837579168</v>
+        <v>0.9498349995401693</v>
       </c>
       <c r="D27" t="n">
-        <v>0.945606837579168</v>
+        <v>0.9498349995401693</v>
       </c>
       <c r="E27" t="n">
-        <v>96.14999999999999</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>62.51000000000001</v>
+        <v>74.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[5, 5, 4, 3, 6]</t>
+          <t>[4, 1, 3, 3, 0]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,22 +1096,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9607529608966914</v>
+        <v>0.9679499260073606</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9607529608966914</v>
+        <v>0.9679499260073606</v>
       </c>
       <c r="E28" t="n">
-        <v>90.34</v>
+        <v>76.36</v>
       </c>
       <c r="F28" t="n">
-        <v>77.34</v>
+        <v>67.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[3, 6, 4, 5, 0]</t>
+          <t>[9, 0, 3, 1, 2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9578031911584716</v>
+        <v>0.9645179083694365</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9578031911584716</v>
+        <v>0.9645179083694365</v>
       </c>
       <c r="E29" t="n">
-        <v>88.13999999999999</v>
+        <v>87.02000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>77.27</v>
+        <v>75.31999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[1, 8, 0, 7, 7]</t>
+          <t>[7, 8, 9, 0, 3]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1144,46 +1144,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9524598999603014</v>
+        <v>0.9496985514487789</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9524598999603014</v>
+        <v>0.9496985514487789</v>
       </c>
       <c r="E30" t="n">
-        <v>96.05</v>
+        <v>82.78999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>66.98999999999999</v>
+        <v>68.84999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[0, 2, 9, 6, 9]</t>
+          <t>[1, 3, 7, 7, 8]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9722854796688929</v>
+        <v>0.9571238684670658</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9722854796688929</v>
+        <v>0.9571238684670658</v>
       </c>
       <c r="E31" t="n">
-        <v>97.04000000000001</v>
+        <v>94.36000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>78.66</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[1, 3, 2, 3, 3]</t>
+          <t>[5, 5, 6, 3, 5]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1192,22 +1192,22 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9697908212367251</v>
+        <v>0.9572498071359344</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9697908212367251</v>
+        <v>0.9572498071359344</v>
       </c>
       <c r="E32" t="n">
-        <v>99.59999999999999</v>
+        <v>79.69999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>55.76</v>
+        <v>55.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[8, 6, 4, 1, 9]</t>
+          <t>[1, 3, 0, 7, 5]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1216,70 +1216,70 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9526446989642593</v>
+        <v>0.965487841692002</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9526446989642593</v>
+        <v>0.965487841692002</v>
       </c>
       <c r="E33" t="n">
-        <v>89.97</v>
+        <v>85.98999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>70.8</v>
+        <v>66.75</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[7, 8, 0, 0, 6]</t>
+          <t>[5, 0, 0, 3, 4]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9565858337680621</v>
+        <v>0.9826608378356052</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9565858337680621</v>
+        <v>0.9826608378356052</v>
       </c>
       <c r="E34" t="n">
-        <v>86.91</v>
+        <v>81.97999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>77.18000000000001</v>
+        <v>79.64</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[8, 1, 4, 5, 1]</t>
+          <t>[5, 2, 7, 4, 5]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9585439224881385</v>
+        <v>0.9784588571556063</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9585439224881385</v>
+        <v>0.9784588571556063</v>
       </c>
       <c r="E35" t="n">
-        <v>96.83999999999999</v>
+        <v>98.87</v>
       </c>
       <c r="F35" t="n">
-        <v>68.25</v>
+        <v>79.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[6, 9, 8, 6, 4]</t>
+          <t>[1, 6, 0, 8, 9]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1288,22 +1288,22 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.932738934219746</v>
+        <v>0.9560937920098417</v>
       </c>
       <c r="D36" t="n">
-        <v>0.932738934219746</v>
+        <v>0.9560937920098417</v>
       </c>
       <c r="E36" t="n">
-        <v>83.45</v>
+        <v>92</v>
       </c>
       <c r="F36" t="n">
-        <v>78.23999999999999</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[6, 3, 0, 5, 1]</t>
+          <t>[5, 3, 1, 2, 7]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1312,22 +1312,22 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9612681594367083</v>
+        <v>0.9666592742073788</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9612681594367083</v>
+        <v>0.9666592742073788</v>
       </c>
       <c r="E37" t="n">
-        <v>92.50999999999999</v>
+        <v>90.89</v>
       </c>
       <c r="F37" t="n">
-        <v>68.90000000000001</v>
+        <v>68.02</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[8, 5, 2, 0, 3]</t>
+          <t>[1, 7, 6, 1, 0]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1336,46 +1336,46 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9613378525427466</v>
+        <v>0.9598931597834343</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9613378525427466</v>
+        <v>0.9598931597834343</v>
       </c>
       <c r="E38" t="n">
-        <v>91.09999999999999</v>
+        <v>98.28999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>71.21000000000001</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[5, 9, 3, 7, 0]</t>
+          <t>[8, 6, 3, 6, 3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9455112048509592</v>
+        <v>0.9733390043037492</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9455112048509592</v>
+        <v>0.9733390043037492</v>
       </c>
       <c r="E39" t="n">
-        <v>95.29999999999998</v>
+        <v>98.5</v>
       </c>
       <c r="F39" t="n">
-        <v>66.57000000000001</v>
+        <v>72.53999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[9, 6, 9, 4, 3]</t>
+          <t>[2, 3, 8, 1, 9]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1384,22 +1384,22 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9349537184962525</v>
+        <v>0.962269442415533</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9349537184962525</v>
+        <v>0.962269442415533</v>
       </c>
       <c r="E40" t="n">
-        <v>89.64</v>
+        <v>92.30000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>67.56</v>
+        <v>72.05</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[5, 6, 5, 5, 9]</t>
+          <t>[5, 2, 2, 5, 8]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1408,70 +1408,70 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9511162267726573</v>
+        <v>0.9635974236475282</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9511162267726573</v>
+        <v>0.9635974236475282</v>
       </c>
       <c r="E41" t="n">
-        <v>89.97999999999999</v>
+        <v>87.47999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>74.84</v>
+        <v>71.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[0, 0, 0, 9, 0]</t>
+          <t>[2, 5, 7, 5, 3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9625670970293839</v>
+        <v>0.9614198771944815</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9625670970293839</v>
+        <v>0.9614198771944815</v>
       </c>
       <c r="E42" t="n">
-        <v>85.79999999999998</v>
+        <v>96.41</v>
       </c>
       <c r="F42" t="n">
-        <v>73.53</v>
+        <v>73.36999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[9, 3, 6, 3, 8]</t>
+          <t>[3, 5, 5, 3, 1]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9469252726417168</v>
+        <v>0.9795343318947648</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9469252726417168</v>
+        <v>0.9795343318947648</v>
       </c>
       <c r="E43" t="n">
-        <v>95.49999999999999</v>
+        <v>99.02</v>
       </c>
       <c r="F43" t="n">
-        <v>66.55000000000001</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[2, 5, 4, 1, 5]</t>
+          <t>[1, 3, 4, 8, 3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1480,70 +1480,70 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9659693557692717</v>
+        <v>0.961070904065761</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9659693557692717</v>
+        <v>0.961070904065761</v>
       </c>
       <c r="E44" t="n">
-        <v>89.69</v>
+        <v>81.64</v>
       </c>
       <c r="F44" t="n">
-        <v>70.77</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[1, 1, 9, 2, 9]</t>
+          <t>[8, 3, 3, 3, 3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9593681563341587</v>
+        <v>0.9654735649004814</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9593681563341587</v>
+        <v>0.9654735649004814</v>
       </c>
       <c r="E45" t="n">
-        <v>93.36</v>
+        <v>84.7</v>
       </c>
       <c r="F45" t="n">
-        <v>52.62</v>
+        <v>63.48</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[1, 8, 4, 0, 9]</t>
+          <t>[3, 0, 6, 4, 3]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9606854652004104</v>
+        <v>0.9666305148838941</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9606854652004104</v>
+        <v>0.9666305148838941</v>
       </c>
       <c r="E46" t="n">
-        <v>92.39</v>
+        <v>83.48</v>
       </c>
       <c r="F46" t="n">
-        <v>69.69999999999999</v>
+        <v>74.97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[0, 0, 2, 3, 7]</t>
+          <t>[7, 1, 2, 4, 7]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1552,46 +1552,46 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9700398168571793</v>
+        <v>0.9610679876065602</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9700398168571793</v>
+        <v>0.9610679876065602</v>
       </c>
       <c r="E47" t="n">
-        <v>88.75999999999999</v>
+        <v>93.44</v>
       </c>
       <c r="F47" t="n">
-        <v>67.91</v>
+        <v>75.92999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[0, 9, 0, 3, 7]</t>
+          <t>[6, 3, 3, 4, 2]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9591081566493019</v>
+        <v>0.9766183545901818</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9591081566493019</v>
+        <v>0.9766183545901818</v>
       </c>
       <c r="E48" t="n">
-        <v>93.09999999999999</v>
+        <v>88.38</v>
       </c>
       <c r="F48" t="n">
-        <v>66.5</v>
+        <v>76.24000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[2, 0, 2, 7, 1]</t>
+          <t>[8, 8, 5, 7, 3]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1600,64 +1600,64 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9645873658836315</v>
+        <v>0.9442396840130945</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9645873658836315</v>
+        <v>0.9442396840130945</v>
       </c>
       <c r="E49" t="n">
-        <v>85.69</v>
+        <v>85.95</v>
       </c>
       <c r="F49" t="n">
-        <v>62.44</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[0, 2, 4, 3, 1]</t>
+          <t>[3, 5, 4, 8, 2]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9691222104347208</v>
+        <v>0.9721787723158904</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9691222104347208</v>
+        <v>0.9721787723158904</v>
       </c>
       <c r="E50" t="n">
-        <v>89.97</v>
+        <v>92.16</v>
       </c>
       <c r="F50" t="n">
-        <v>66.34999999999999</v>
+        <v>77.64</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[5, 1, 7, 9, 5]</t>
+          <t>[3, 4, 2, 5, 4]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9490700665820639</v>
+        <v>0.9772332609903681</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9490700665820639</v>
+        <v>0.9772332609903681</v>
       </c>
       <c r="E51" t="n">
-        <v>96.91999999999999</v>
+        <v>86.24000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>64.58</v>
+        <v>79.3</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[7, 1, 2, 7, 9]</t>
+          <t>[9, 7, 4, 1, 6]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,70 +472,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9570717966998844</v>
+        <v>0.9575769639087939</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9570717966998844</v>
+        <v>0.9575769639087939</v>
       </c>
       <c r="E2" t="n">
-        <v>99.10000000000001</v>
+        <v>83.98</v>
       </c>
       <c r="F2" t="n">
-        <v>75.69</v>
+        <v>70.44999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[0, 2, 8, 2, 8]</t>
+          <t>[7, 1, 5, 3, 2]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9648980383858681</v>
+        <v>0.9749449340037779</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9648980383858681</v>
+        <v>0.9749449340037779</v>
       </c>
       <c r="E3" t="n">
-        <v>86.96000000000001</v>
+        <v>95.31</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>78.72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[8, 1, 0, 2, 8]</t>
+          <t>[2, 6, 8, 1, 0]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9650316968973885</v>
+        <v>0.9775216889699516</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9650316968973885</v>
+        <v>0.9775216889699516</v>
       </c>
       <c r="E4" t="n">
-        <v>92.66</v>
+        <v>92.44</v>
       </c>
       <c r="F4" t="n">
-        <v>77.44</v>
+        <v>75.37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[4, 7, 5, 4, 4]</t>
+          <t>[2, 7, 5, 1, 4]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,94 +544,94 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9546196165581458</v>
+        <v>0.9628756559922057</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9546196165581458</v>
+        <v>0.9628756559922057</v>
       </c>
       <c r="E5" t="n">
-        <v>73.56999999999999</v>
+        <v>86.54000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>70.02</v>
+        <v>70.36999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0, 3, 4, 5, 3]</t>
+          <t>[0, 5, 4, 4, 6]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9691606067341996</v>
+        <v>0.964483518717635</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9691606067341996</v>
+        <v>0.964483518717635</v>
       </c>
       <c r="E6" t="n">
-        <v>81.88</v>
+        <v>81.49000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>72.83</v>
+        <v>70.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[9, 3, 3, 5, 6]</t>
+          <t>[3, 3, 5, 9, 8]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.962043132865551</v>
+        <v>0.9754194461194809</v>
       </c>
       <c r="D7" t="n">
-        <v>0.962043132865551</v>
+        <v>0.9754194461194809</v>
       </c>
       <c r="E7" t="n">
-        <v>96.64</v>
+        <v>98.78</v>
       </c>
       <c r="F7" t="n">
-        <v>71.81999999999999</v>
+        <v>73.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[4, 6, 1, 6, 2]</t>
+          <t>[3, 8, 1, 6, 3]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9553018482827768</v>
+        <v>0.9799708272229297</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9553018482827768</v>
+        <v>0.9799708272229297</v>
       </c>
       <c r="E8" t="n">
-        <v>90.46000000000001</v>
+        <v>87.38</v>
       </c>
       <c r="F8" t="n">
-        <v>74.78999999999999</v>
+        <v>67.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[6, 3, 8, 4, 5]</t>
+          <t>[4, 5, 5, 3, 8]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,22 +640,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9766190601830285</v>
+        <v>0.976648554604037</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9766190601830285</v>
+        <v>0.976648554604037</v>
       </c>
       <c r="E9" t="n">
-        <v>96.36000000000001</v>
+        <v>98.02999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>75.60000000000001</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[8, 0, 6, 6, 6]</t>
+          <t>[1, 0, 5, 8, 4]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -664,142 +664,142 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9509969520812122</v>
+        <v>0.9632122596717219</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9509969520812122</v>
+        <v>0.9632122596717219</v>
       </c>
       <c r="E10" t="n">
-        <v>85.38</v>
+        <v>77.97</v>
       </c>
       <c r="F10" t="n">
-        <v>69.36</v>
+        <v>61.64999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[3, 8, 3, 6, 5]</t>
+          <t>[0, 6, 6, 5, 6]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.958128180595092</v>
+        <v>0.9778767757856017</v>
       </c>
       <c r="D11" t="n">
-        <v>0.958128180595092</v>
+        <v>0.9778767757856017</v>
       </c>
       <c r="E11" t="n">
-        <v>95.3</v>
+        <v>79.8</v>
       </c>
       <c r="F11" t="n">
-        <v>68.25999999999999</v>
+        <v>75.44</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[3, 5, 4, 2, 6]</t>
+          <t>[7, 5, 8, 5, 7]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.979045312092373</v>
+        <v>0.9516566913505965</v>
       </c>
       <c r="D12" t="n">
-        <v>0.979045312092373</v>
+        <v>0.9516566913505965</v>
       </c>
       <c r="E12" t="n">
-        <v>91.38</v>
+        <v>67.03</v>
       </c>
       <c r="F12" t="n">
-        <v>77.12</v>
+        <v>64.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 6, 3]</t>
+          <t>[1, 8, 0, 3, 7]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9734705725199746</v>
+        <v>0.9643285474809292</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9734705725199746</v>
+        <v>0.9643285474809292</v>
       </c>
       <c r="E13" t="n">
-        <v>89.91999999999999</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>64.72</v>
+        <v>62.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[1, 4, 2, 0, 6]</t>
+          <t>[2, 7, 3, 5, 8]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9692439808251494</v>
+        <v>0.979252657005949</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9692439808251494</v>
+        <v>0.979252657005949</v>
       </c>
       <c r="E14" t="n">
-        <v>85.96000000000001</v>
+        <v>91.78</v>
       </c>
       <c r="F14" t="n">
-        <v>78.58</v>
+        <v>76.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[8, 3, 8, 3, 8]</t>
+          <t>[8, 0, 8, 1, 2]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9658779296708239</v>
+        <v>0.9722003215075553</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9658779296708239</v>
+        <v>0.9722003215075553</v>
       </c>
       <c r="E15" t="n">
-        <v>95.46000000000001</v>
+        <v>93.02000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>70.56</v>
+        <v>72.48999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[2, 6, 1, 8, 9]</t>
+          <t>[2, 9, 0, 1, 7]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,46 +808,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9544835383543275</v>
+        <v>0.9636736327304435</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9544835383543275</v>
+        <v>0.9636736327304435</v>
       </c>
       <c r="E16" t="n">
-        <v>96.90000000000001</v>
+        <v>85.52000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>75.06999999999999</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 5, 0, 8, 5]</t>
+          <t>[3, 2, 3, 8, 8]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9815692689145882</v>
+        <v>0.9766050042697145</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9815692689145882</v>
+        <v>0.9766050042697145</v>
       </c>
       <c r="E17" t="n">
-        <v>96.18000000000001</v>
+        <v>95.27</v>
       </c>
       <c r="F17" t="n">
-        <v>75.59</v>
+        <v>71.46000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[6, 9, 6, 5, 7]</t>
+          <t>[7, 5, 5, 8, 3]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,46 +856,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9441126096099557</v>
+        <v>0.9524556978864788</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9441126096099557</v>
+        <v>0.9524556978864788</v>
       </c>
       <c r="E18" t="n">
-        <v>89.50999999999999</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>65.42</v>
+        <v>60.70000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[4, 1, 6, 0, 8]</t>
+          <t>[6, 8, 0, 3, 2]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9620855629054981</v>
+        <v>0.9760522623448843</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9620855629054981</v>
+        <v>0.9760522623448843</v>
       </c>
       <c r="E19" t="n">
-        <v>86.34</v>
+        <v>90.78999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>74.04000000000001</v>
+        <v>76.98000000000002</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[1, 6, 8, 0, 6]</t>
+          <t>[2, 8, 3, 6, 7]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -904,46 +904,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9591489032530607</v>
+        <v>0.9585811551658958</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9591489032530607</v>
+        <v>0.9585811551658958</v>
       </c>
       <c r="E20" t="n">
-        <v>91.47999999999999</v>
+        <v>77.53</v>
       </c>
       <c r="F20" t="n">
-        <v>71.86</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[3, 0, 3, 3, 5]</t>
+          <t>[6, 5, 1, 2, 6]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9858289534308138</v>
+        <v>0.9787001434134972</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9858289534308138</v>
+        <v>0.9787001434134972</v>
       </c>
       <c r="E21" t="n">
-        <v>98.64</v>
+        <v>95.7</v>
       </c>
       <c r="F21" t="n">
-        <v>78.5</v>
+        <v>74.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[9, 4, 1, 3, 9]</t>
+          <t>[1, 9, 4, 4, 6]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,46 +952,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9589646194726471</v>
+        <v>0.9602998146539358</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9589646194726471</v>
+        <v>0.9602998146539358</v>
       </c>
       <c r="E22" t="n">
-        <v>86.5</v>
+        <v>92.07000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>70.59</v>
+        <v>70.74000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[7, 3, 2, 5, 6]</t>
+          <t>[4, 0, 5, 8, 8]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9756109033612697</v>
+        <v>0.9605205819253021</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9756109033612697</v>
+        <v>0.9605205819253021</v>
       </c>
       <c r="E23" t="n">
-        <v>98.00999999999999</v>
+        <v>75.55</v>
       </c>
       <c r="F23" t="n">
-        <v>75.51000000000001</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[3, 2, 5, 5, 6]</t>
+          <t>[8, 6, 2, 2, 9]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1000,94 +1000,94 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9635044104364154</v>
+        <v>0.9598347031171028</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9635044104364154</v>
+        <v>0.9598347031171028</v>
       </c>
       <c r="E24" t="n">
-        <v>81.69999999999999</v>
+        <v>93.33</v>
       </c>
       <c r="F24" t="n">
-        <v>62.81</v>
+        <v>67.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[7, 8, 5, 8, 5]</t>
+          <t>[1, 6, 3, 1, 6]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.943255770381941</v>
+        <v>0.9814285683659641</v>
       </c>
       <c r="D25" t="n">
-        <v>0.943255770381941</v>
+        <v>0.9814285683659641</v>
       </c>
       <c r="E25" t="n">
-        <v>88.94999999999999</v>
+        <v>87.27</v>
       </c>
       <c r="F25" t="n">
-        <v>62.38</v>
+        <v>72.80000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[4, 5, 6, 3, 8]</t>
+          <t>[1, 5, 8, 7, 2]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9567911819564763</v>
+        <v>0.9741403970846433</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9567911819564763</v>
+        <v>0.9741403970846433</v>
       </c>
       <c r="E26" t="n">
-        <v>78.53999999999999</v>
+        <v>96.19</v>
       </c>
       <c r="F26" t="n">
-        <v>62.59</v>
+        <v>74.07000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[7, 8, 9, 0, 1]</t>
+          <t>[8, 5, 7, 4, 2]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9498349995401693</v>
+        <v>0.97582827780242</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9498349995401693</v>
+        <v>0.97582827780242</v>
       </c>
       <c r="E27" t="n">
-        <v>93.48999999999999</v>
+        <v>98.17000000000002</v>
       </c>
       <c r="F27" t="n">
-        <v>74.37</v>
+        <v>78.28</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[4, 1, 3, 3, 0]</t>
+          <t>[4, 6, 9, 3, 7]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,46 +1096,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9679499260073606</v>
+        <v>0.9559101397455387</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9679499260073606</v>
+        <v>0.9559101397455387</v>
       </c>
       <c r="E28" t="n">
-        <v>76.36</v>
+        <v>82.33000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>67.48</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[9, 0, 3, 1, 2]</t>
+          <t>[6, 1, 5, 6, 2]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9645179083694365</v>
+        <v>0.9747554093341179</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9645179083694365</v>
+        <v>0.9747554093341179</v>
       </c>
       <c r="E29" t="n">
-        <v>87.02000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>75.31999999999999</v>
+        <v>76.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[7, 8, 9, 0, 3]</t>
+          <t>[2, 1, 0, 7, 9]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1144,22 +1144,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9496985514487789</v>
+        <v>0.965999015751979</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9496985514487789</v>
+        <v>0.965999015751979</v>
       </c>
       <c r="E30" t="n">
-        <v>82.78999999999999</v>
+        <v>85.52</v>
       </c>
       <c r="F30" t="n">
-        <v>68.84999999999999</v>
+        <v>70.42</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[1, 3, 7, 7, 8]</t>
+          <t>[2, 6, 7, 4, 4]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1168,22 +1168,22 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9571238684670658</v>
+        <v>0.9608543349412437</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9571238684670658</v>
+        <v>0.9608543349412437</v>
       </c>
       <c r="E31" t="n">
-        <v>94.36000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>66.19</v>
+        <v>77.53999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[5, 5, 6, 3, 5]</t>
+          <t>[3, 0, 1, 7, 2]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1192,70 +1192,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9572498071359344</v>
+        <v>0.9664981263421305</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9572498071359344</v>
+        <v>0.9664981263421305</v>
       </c>
       <c r="E32" t="n">
-        <v>79.69999999999999</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>55.61</v>
+        <v>68.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[1, 3, 0, 7, 5]</t>
+          <t>[8, 7, 2, 5, 2]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.965487841692002</v>
+        <v>0.9763607018510175</v>
       </c>
       <c r="D33" t="n">
-        <v>0.965487841692002</v>
+        <v>0.9763607018510175</v>
       </c>
       <c r="E33" t="n">
-        <v>85.98999999999999</v>
+        <v>99.67000000000002</v>
       </c>
       <c r="F33" t="n">
-        <v>66.75</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[5, 0, 0, 3, 4]</t>
+          <t>[6, 8, 5, 0, 8]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9826608378356052</v>
+        <v>0.9762206678472279</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9826608378356052</v>
+        <v>0.9762206678472279</v>
       </c>
       <c r="E34" t="n">
-        <v>81.97999999999999</v>
+        <v>81.02</v>
       </c>
       <c r="F34" t="n">
-        <v>79.64</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[5, 2, 7, 4, 5]</t>
+          <t>[8, 4, 3, 8, 8]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,262 +1264,262 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9784588571556063</v>
+        <v>0.974793473054872</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9784588571556063</v>
+        <v>0.974793473054872</v>
       </c>
       <c r="E35" t="n">
-        <v>98.87</v>
+        <v>91.89</v>
       </c>
       <c r="F35" t="n">
-        <v>79.45</v>
+        <v>66.15000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[1, 6, 0, 8, 9]</t>
+          <t>[1, 3, 8, 7, 8]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9560937920098417</v>
+        <v>0.9631815559045381</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9560937920098417</v>
+        <v>0.9631815559045381</v>
       </c>
       <c r="E36" t="n">
-        <v>92</v>
+        <v>86.22</v>
       </c>
       <c r="F36" t="n">
-        <v>73.8</v>
+        <v>67.28999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[5, 3, 1, 2, 7]</t>
+          <t>[8, 1, 7, 0, 6]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9666592742073788</v>
+        <v>0.9814111785201955</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9666592742073788</v>
+        <v>0.9814111785201955</v>
       </c>
       <c r="E37" t="n">
-        <v>90.89</v>
+        <v>82.12</v>
       </c>
       <c r="F37" t="n">
-        <v>68.02</v>
+        <v>79.00999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[1, 7, 6, 1, 0]</t>
+          <t>[2, 9, 1, 8, 0]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9598931597834343</v>
+        <v>0.9595084561211591</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9598931597834343</v>
+        <v>0.9595084561211591</v>
       </c>
       <c r="E38" t="n">
-        <v>98.28999999999999</v>
+        <v>99.66</v>
       </c>
       <c r="F38" t="n">
-        <v>74.41</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[8, 6, 3, 6, 3]</t>
+          <t>[8, 1, 3, 0, 6]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9733390043037492</v>
+        <v>0.9765909376734885</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9733390043037492</v>
+        <v>0.9765909376734885</v>
       </c>
       <c r="E39" t="n">
-        <v>98.5</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>72.53999999999999</v>
+        <v>69.91999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[2, 3, 8, 1, 9]</t>
+          <t>[0, 1, 1, 5, 8]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.962269442415533</v>
+        <v>0.9830892507309017</v>
       </c>
       <c r="D40" t="n">
-        <v>0.962269442415533</v>
+        <v>0.9830892507309017</v>
       </c>
       <c r="E40" t="n">
-        <v>92.30000000000001</v>
+        <v>90.03999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>72.05</v>
+        <v>66.77999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[5, 2, 2, 5, 8]</t>
+          <t>[6, 4, 1, 4, 5]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9635974236475282</v>
+        <v>0.9673221225975912</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9635974236475282</v>
+        <v>0.9673221225975912</v>
       </c>
       <c r="E41" t="n">
-        <v>87.47999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="F41" t="n">
-        <v>71.41</v>
+        <v>79.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[2, 5, 7, 5, 3]</t>
+          <t>[9, 0, 6, 3, 6]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9614198771944815</v>
+        <v>0.9571752759082153</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9614198771944815</v>
+        <v>0.9571752759082153</v>
       </c>
       <c r="E42" t="n">
-        <v>96.41</v>
+        <v>74.72</v>
       </c>
       <c r="F42" t="n">
-        <v>73.36999999999999</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[3, 5, 5, 3, 1]</t>
+          <t>[4, 1, 0, 5, 5]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9795343318947648</v>
+        <v>0.9817663159588216</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9795343318947648</v>
+        <v>0.9817663159588216</v>
       </c>
       <c r="E43" t="n">
-        <v>99.02</v>
+        <v>91.34</v>
       </c>
       <c r="F43" t="n">
-        <v>68.09999999999999</v>
+        <v>75.16999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[1, 3, 4, 8, 3]</t>
+          <t>[3, 6, 3, 0, 6]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.961070904065761</v>
+        <v>0.9793251146054944</v>
       </c>
       <c r="D44" t="n">
-        <v>0.961070904065761</v>
+        <v>0.9793251146054944</v>
       </c>
       <c r="E44" t="n">
-        <v>81.64</v>
+        <v>83.67</v>
       </c>
       <c r="F44" t="n">
-        <v>64.20999999999999</v>
+        <v>76.75999999999999</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[8, 3, 3, 3, 3]</t>
+          <t>[8, 2, 6, 3, 7]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9654735649004814</v>
+        <v>0.9729944194921889</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9654735649004814</v>
+        <v>0.9729944194921889</v>
       </c>
       <c r="E45" t="n">
-        <v>84.7</v>
+        <v>92.35000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>63.48</v>
+        <v>78.82000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[3, 0, 6, 4, 3]</t>
+          <t>[3, 3, 1, 8, 3]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1528,118 +1528,118 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9666305148838941</v>
+        <v>0.9659736259862318</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9666305148838941</v>
+        <v>0.9659736259862318</v>
       </c>
       <c r="E46" t="n">
-        <v>83.48</v>
+        <v>89.8</v>
       </c>
       <c r="F46" t="n">
-        <v>74.97</v>
+        <v>69.63000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[7, 1, 2, 4, 7]</t>
+          <t>[6, 1, 1, 8, 2]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9610679876065602</v>
+        <v>0.9782390510795363</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9610679876065602</v>
+        <v>0.9782390510795363</v>
       </c>
       <c r="E47" t="n">
-        <v>93.44</v>
+        <v>96.03999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>75.92999999999999</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[6, 3, 3, 4, 2]</t>
+          <t>[1, 6, 2, 8, 0]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9766183545901818</v>
+        <v>0.9610856660032717</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9766183545901818</v>
+        <v>0.9610856660032717</v>
       </c>
       <c r="E48" t="n">
-        <v>88.38</v>
+        <v>79.27000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>76.24000000000001</v>
+        <v>62.41000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[8, 8, 5, 7, 3]</t>
+          <t>[6, 6, 4, 1, 1]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9442396840130945</v>
+        <v>0.9650739201448919</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9442396840130945</v>
+        <v>0.9650739201448919</v>
       </c>
       <c r="E49" t="n">
-        <v>85.95</v>
+        <v>96.62</v>
       </c>
       <c r="F49" t="n">
-        <v>61.5</v>
+        <v>74.63999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[3, 5, 4, 8, 2]</t>
+          <t>[5, 0, 8, 2, 1]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9721787723158904</v>
+        <v>0.9813566976421711</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9721787723158904</v>
+        <v>0.9813566976421711</v>
       </c>
       <c r="E50" t="n">
-        <v>92.16</v>
+        <v>93.86</v>
       </c>
       <c r="F50" t="n">
-        <v>77.64</v>
+        <v>70.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[3, 4, 2, 5, 4]</t>
+          <t>[6, 1, 1, 8, 3]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9772332609903681</v>
+        <v>0.9781502750851661</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9772332609903681</v>
+        <v>0.9781502750851661</v>
       </c>
       <c r="E51" t="n">
-        <v>86.24000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>79.3</v>
+        <v>69.17999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[9, 7, 4, 1, 6]</t>
+          <t>[3, 7, 1, 2, 3]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,22 +472,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9575769639087939</v>
+        <v>0.9642717353494864</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9575769639087939</v>
+        <v>0.9642717353494864</v>
       </c>
       <c r="E2" t="n">
-        <v>83.98</v>
+        <v>76.22999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>70.44999999999999</v>
+        <v>61.12</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[7, 1, 5, 3, 2]</t>
+          <t>[3, 2, 3, 2, 5]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,46 +496,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9749449340037779</v>
+        <v>0.9820593169868728</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9749449340037779</v>
+        <v>0.9820593169868728</v>
       </c>
       <c r="E3" t="n">
-        <v>95.31</v>
+        <v>98.13</v>
       </c>
       <c r="F3" t="n">
-        <v>78.72</v>
+        <v>75.19999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[2, 6, 8, 1, 0]</t>
+          <t>[1, 0, 3, 7, 7]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9775216889699516</v>
+        <v>0.9644143822493041</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9775216889699516</v>
+        <v>0.9644143822493041</v>
       </c>
       <c r="E4" t="n">
-        <v>92.44</v>
+        <v>78.88</v>
       </c>
       <c r="F4" t="n">
-        <v>75.37</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[2, 7, 5, 1, 4]</t>
+          <t>[1, 8, 1, 5, 7]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -544,22 +544,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9628756559922057</v>
+        <v>0.9584566050560265</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9628756559922057</v>
+        <v>0.9584566050560265</v>
       </c>
       <c r="E5" t="n">
-        <v>86.54000000000001</v>
+        <v>81.05</v>
       </c>
       <c r="F5" t="n">
-        <v>70.36999999999999</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[0, 5, 4, 4, 6]</t>
+          <t>[6, 0, 1, 0, 8]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -568,94 +568,94 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.964483518717635</v>
+        <v>0.9664406653902152</v>
       </c>
       <c r="D6" t="n">
-        <v>0.964483518717635</v>
+        <v>0.9664406653902152</v>
       </c>
       <c r="E6" t="n">
-        <v>81.49000000000001</v>
+        <v>95.66</v>
       </c>
       <c r="F6" t="n">
-        <v>70.91</v>
+        <v>61.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[3, 3, 5, 9, 8]</t>
+          <t>[6, 6, 9, 1, 5]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9754194461194809</v>
+        <v>0.9440684919833869</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9754194461194809</v>
+        <v>0.9440684919833869</v>
       </c>
       <c r="E7" t="n">
-        <v>98.78</v>
+        <v>84.75</v>
       </c>
       <c r="F7" t="n">
-        <v>73.91</v>
+        <v>64.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[3, 8, 1, 6, 3]</t>
+          <t>[3, 9, 9, 3, 4]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9799708272229297</v>
+        <v>0.9691628923378027</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9799708272229297</v>
+        <v>0.9691628923378027</v>
       </c>
       <c r="E8" t="n">
-        <v>87.38</v>
+        <v>92.93000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>67.17</v>
+        <v>68.50999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[4, 5, 5, 3, 8]</t>
+          <t>[0, 2, 9, 8, 1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.976648554604037</v>
+        <v>0.957045461419307</v>
       </c>
       <c r="D9" t="n">
-        <v>0.976648554604037</v>
+        <v>0.957045461419307</v>
       </c>
       <c r="E9" t="n">
-        <v>98.02999999999999</v>
+        <v>91.68999999999998</v>
       </c>
       <c r="F9" t="n">
-        <v>77.40000000000001</v>
+        <v>63.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[1, 0, 5, 8, 4]</t>
+          <t>[0, 6, 2, 0, 8]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -664,430 +664,430 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9632122596717219</v>
+        <v>0.966600812887534</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9632122596717219</v>
+        <v>0.966600812887534</v>
       </c>
       <c r="E10" t="n">
-        <v>77.97</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>61.64999999999999</v>
+        <v>64.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[0, 6, 6, 5, 6]</t>
+          <t>[3, 5, 9, 6, 9]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9778767757856017</v>
+        <v>0.9685490132896067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9778767757856017</v>
+        <v>0.9685490132896067</v>
       </c>
       <c r="E11" t="n">
-        <v>79.8</v>
+        <v>89.61</v>
       </c>
       <c r="F11" t="n">
-        <v>75.44</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[7, 5, 8, 5, 7]</t>
+          <t>[3, 9, 9, 3, 1]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9516566913505965</v>
+        <v>0.96996535768801</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9516566913505965</v>
+        <v>0.96996535768801</v>
       </c>
       <c r="E12" t="n">
-        <v>67.03</v>
+        <v>89.63</v>
       </c>
       <c r="F12" t="n">
-        <v>64.44</v>
+        <v>63.84</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[1, 8, 0, 3, 7]</t>
+          <t>[2, 7, 3, 3, 3]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9643285474809292</v>
+        <v>0.9753204729502393</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9643285474809292</v>
+        <v>0.9753204729502393</v>
       </c>
       <c r="E13" t="n">
-        <v>70.98999999999999</v>
+        <v>88.53</v>
       </c>
       <c r="F13" t="n">
-        <v>62.31</v>
+        <v>73.33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[2, 7, 3, 5, 8]</t>
+          <t>[6, 3, 9, 5, 5]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.979252657005949</v>
+        <v>0.9623988801991917</v>
       </c>
       <c r="D14" t="n">
-        <v>0.979252657005949</v>
+        <v>0.9623988801991917</v>
       </c>
       <c r="E14" t="n">
-        <v>91.78</v>
+        <v>88.75</v>
       </c>
       <c r="F14" t="n">
-        <v>76.34</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[8, 0, 8, 1, 2]</t>
+          <t>[3, 4, 8, 3, 6]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9722003215075553</v>
+        <v>0.9580561739206084</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9722003215075553</v>
+        <v>0.9580561739206084</v>
       </c>
       <c r="E15" t="n">
-        <v>93.02000000000001</v>
+        <v>79.62</v>
       </c>
       <c r="F15" t="n">
-        <v>72.48999999999999</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[2, 9, 0, 1, 7]</t>
+          <t>[9, 7, 0, 6, 3]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9636736327304435</v>
+        <v>0.9649279441648226</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9636736327304435</v>
+        <v>0.9649279441648226</v>
       </c>
       <c r="E16" t="n">
-        <v>85.52000000000001</v>
+        <v>96.25</v>
       </c>
       <c r="F16" t="n">
-        <v>70.42</v>
+        <v>74.25999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[3, 2, 3, 8, 8]</t>
+          <t>[3, 0, 5, 3, 9]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9766050042697145</v>
+        <v>0.9824194287585958</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9766050042697145</v>
+        <v>0.9824194287585958</v>
       </c>
       <c r="E17" t="n">
-        <v>95.27</v>
+        <v>91.53</v>
       </c>
       <c r="F17" t="n">
-        <v>71.46000000000001</v>
+        <v>64.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[7, 5, 5, 8, 3]</t>
+          <t>[8, 3, 8, 5, 1]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9524556978864788</v>
+        <v>0.952510323455138</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9524556978864788</v>
+        <v>0.952510323455138</v>
       </c>
       <c r="E18" t="n">
-        <v>69.06999999999999</v>
+        <v>96.03999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>60.70000000000001</v>
+        <v>78.18000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[6, 8, 0, 3, 2]</t>
+          <t>[1, 7, 6, 9, 9]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9760522623448843</v>
+        <v>0.9695458798413245</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9760522623448843</v>
+        <v>0.9695458798413245</v>
       </c>
       <c r="E19" t="n">
-        <v>90.78999999999999</v>
+        <v>96.92999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>76.98000000000002</v>
+        <v>78.10999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[2, 8, 3, 6, 7]</t>
+          <t>[5, 9, 3, 9, 7]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9585811551658958</v>
+        <v>0.9715651324788382</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9585811551658958</v>
+        <v>0.9715651324788382</v>
       </c>
       <c r="E20" t="n">
-        <v>77.53</v>
+        <v>88.28999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>66.44</v>
+        <v>76.06999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[6, 5, 1, 2, 6]</t>
+          <t>[3, 3, 0, 1, 8]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9787001434134972</v>
+        <v>0.9833681855800357</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9787001434134972</v>
+        <v>0.9833681855800357</v>
       </c>
       <c r="E21" t="n">
-        <v>95.7</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>74.53</v>
+        <v>65.97999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[1, 9, 4, 4, 6]</t>
+          <t>[5, 2, 3, 3, 1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9602998146539358</v>
+        <v>0.9823661078409949</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9602998146539358</v>
+        <v>0.9823661078409949</v>
       </c>
       <c r="E22" t="n">
-        <v>92.07000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="F22" t="n">
-        <v>70.74000000000001</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[4, 0, 5, 8, 8]</t>
+          <t>[3, 6, 1, 3, 0]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9605205819253021</v>
+        <v>0.9822177434728412</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9605205819253021</v>
+        <v>0.9822177434728412</v>
       </c>
       <c r="E23" t="n">
-        <v>75.55</v>
+        <v>96.73</v>
       </c>
       <c r="F23" t="n">
-        <v>60.22</v>
+        <v>63.73</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[8, 6, 2, 2, 9]</t>
+          <t>[3, 3, 8, 1, 7]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9598347031171028</v>
+        <v>0.9805894632163757</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9598347031171028</v>
+        <v>0.9805894632163757</v>
       </c>
       <c r="E24" t="n">
-        <v>93.33</v>
+        <v>84.2</v>
       </c>
       <c r="F24" t="n">
-        <v>67.77</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[1, 6, 3, 1, 6]</t>
+          <t>[1, 3, 3, 7, 6]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9814285683659641</v>
+        <v>0.9745446904517699</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9814285683659641</v>
+        <v>0.9745446904517699</v>
       </c>
       <c r="E25" t="n">
-        <v>87.27</v>
+        <v>86.61</v>
       </c>
       <c r="F25" t="n">
-        <v>72.80000000000001</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[1, 5, 8, 7, 2]</t>
+          <t>[3, 3, 1, 6, 3]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9741403970846433</v>
+        <v>0.966061352809401</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9741403970846433</v>
+        <v>0.966061352809401</v>
       </c>
       <c r="E26" t="n">
-        <v>96.19</v>
+        <v>87.06</v>
       </c>
       <c r="F26" t="n">
-        <v>74.07000000000001</v>
+        <v>62.96</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[8, 5, 7, 4, 2]</t>
+          <t>[9, 8, 6, 8, 1]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.97582827780242</v>
+        <v>0.9333069323797059</v>
       </c>
       <c r="D27" t="n">
-        <v>0.97582827780242</v>
+        <v>0.9333069323797059</v>
       </c>
       <c r="E27" t="n">
-        <v>98.17000000000002</v>
+        <v>81.66</v>
       </c>
       <c r="F27" t="n">
-        <v>78.28</v>
+        <v>69.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[4, 6, 9, 3, 7]</t>
+          <t>[5, 9, 6, 1, 5]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,70 +1096,70 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9559101397455387</v>
+        <v>0.949860044480776</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9559101397455387</v>
+        <v>0.949860044480776</v>
       </c>
       <c r="E28" t="n">
-        <v>82.33000000000001</v>
+        <v>83.02</v>
       </c>
       <c r="F28" t="n">
-        <v>72.06</v>
+        <v>64.84999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[6, 1, 5, 6, 2]</t>
+          <t>[9, 3, 8, 9, 9]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9747554093341179</v>
+        <v>0.9355456590131316</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9747554093341179</v>
+        <v>0.9355456590131316</v>
       </c>
       <c r="E29" t="n">
-        <v>92.40000000000001</v>
+        <v>75.41999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>76.72</v>
+        <v>61.72</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[2, 1, 0, 7, 9]</t>
+          <t>[3, 3, 5, 9, 9]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.965999015751979</v>
+        <v>0.9747568860362821</v>
       </c>
       <c r="D30" t="n">
-        <v>0.965999015751979</v>
+        <v>0.9747568860362821</v>
       </c>
       <c r="E30" t="n">
-        <v>85.52</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>70.42</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[2, 6, 7, 4, 4]</t>
+          <t>[3, 8, 7, 0, 4]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1168,46 +1168,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9608543349412437</v>
+        <v>0.956850144670965</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9608543349412437</v>
+        <v>0.956850144670965</v>
       </c>
       <c r="E31" t="n">
-        <v>90.40000000000001</v>
+        <v>84.53</v>
       </c>
       <c r="F31" t="n">
-        <v>77.53999999999999</v>
+        <v>68.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[3, 0, 1, 7, 2]</t>
+          <t>[9, 8, 0, 5, 3]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9664981263421305</v>
+        <v>0.9721802064911383</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9664981263421305</v>
+        <v>0.9721802064911383</v>
       </c>
       <c r="E32" t="n">
-        <v>79.65000000000001</v>
+        <v>95.33</v>
       </c>
       <c r="F32" t="n">
-        <v>68.61</v>
+        <v>77.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[8, 7, 2, 5, 2]</t>
+          <t>[6, 3, 7, 3, 4]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1216,214 +1216,214 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9763607018510175</v>
+        <v>0.9668171433008867</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9763607018510175</v>
+        <v>0.9668171433008867</v>
       </c>
       <c r="E33" t="n">
-        <v>99.67000000000002</v>
+        <v>89.91</v>
       </c>
       <c r="F33" t="n">
-        <v>79.59999999999999</v>
+        <v>74.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[6, 8, 5, 0, 8]</t>
+          <t>[2, 5, 0, 6, 1]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9762206678472279</v>
+        <v>0.9615991715457538</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9762206678472279</v>
+        <v>0.9615991715457538</v>
       </c>
       <c r="E34" t="n">
-        <v>81.02</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>69.73</v>
+        <v>63.39999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[8, 4, 3, 8, 8]</t>
+          <t>[3, 3, 6, 8, 5]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.974793473054872</v>
+        <v>0.9726512287960631</v>
       </c>
       <c r="D35" t="n">
-        <v>0.974793473054872</v>
+        <v>0.9726512287960631</v>
       </c>
       <c r="E35" t="n">
-        <v>91.89</v>
+        <v>88.94</v>
       </c>
       <c r="F35" t="n">
-        <v>66.15000000000001</v>
+        <v>76.36999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[1, 3, 8, 7, 8]</t>
+          <t>[3, 9, 0, 6, 9]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9631815559045381</v>
+        <v>0.9493633777225902</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9631815559045381</v>
+        <v>0.9493633777225902</v>
       </c>
       <c r="E36" t="n">
-        <v>86.22</v>
+        <v>84.06</v>
       </c>
       <c r="F36" t="n">
-        <v>67.28999999999999</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[8, 1, 7, 0, 6]</t>
+          <t>[8, 7, 3, 1, 3]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9814111785201955</v>
+        <v>0.9733501624639787</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9814111785201955</v>
+        <v>0.9733501624639787</v>
       </c>
       <c r="E37" t="n">
-        <v>82.12</v>
+        <v>83.75</v>
       </c>
       <c r="F37" t="n">
-        <v>79.00999999999999</v>
+        <v>79.66999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[2, 9, 1, 8, 0]</t>
+          <t>[1, 3, 5, 8, 9]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9595084561211591</v>
+        <v>0.9580344551493011</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9595084561211591</v>
+        <v>0.9580344551493011</v>
       </c>
       <c r="E38" t="n">
-        <v>99.66</v>
+        <v>78.03</v>
       </c>
       <c r="F38" t="n">
-        <v>77.34</v>
+        <v>62.76</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[8, 1, 3, 0, 6]</t>
+          <t>[4, 0, 4, 7, 3]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9765909376734885</v>
+        <v>0.9604839881543316</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9765909376734885</v>
+        <v>0.9604839881543316</v>
       </c>
       <c r="E39" t="n">
-        <v>87.84999999999999</v>
+        <v>92.83999999999999</v>
       </c>
       <c r="F39" t="n">
-        <v>69.91999999999999</v>
+        <v>68.44999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[0, 1, 1, 5, 8]</t>
+          <t>[3, 3, 3, 9, 8]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9830892507309017</v>
+        <v>0.981388927422317</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9830892507309017</v>
+        <v>0.981388927422317</v>
       </c>
       <c r="E40" t="n">
-        <v>90.03999999999999</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="F40" t="n">
-        <v>66.77999999999999</v>
+        <v>75.3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[6, 4, 1, 4, 5]</t>
+          <t>[1, 2, 9, 9, 0]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9673221225975912</v>
+        <v>0.9536192500544003</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9673221225975912</v>
+        <v>0.9536192500544003</v>
       </c>
       <c r="E41" t="n">
-        <v>98.8</v>
+        <v>93.23</v>
       </c>
       <c r="F41" t="n">
-        <v>79.41</v>
+        <v>59.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[9, 0, 6, 3, 6]</t>
+          <t>[2, 0, 8, 9, 3]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1432,232 +1432,232 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9571752759082153</v>
+        <v>0.9567682933163573</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9571752759082153</v>
+        <v>0.9567682933163573</v>
       </c>
       <c r="E42" t="n">
-        <v>74.72</v>
+        <v>84.77999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>66.19</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[4, 1, 0, 5, 5]</t>
+          <t>[4, 3, 7, 2, 4]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9817663159588216</v>
+        <v>0.9596669991789137</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9817663159588216</v>
+        <v>0.9596669991789137</v>
       </c>
       <c r="E43" t="n">
-        <v>91.34</v>
+        <v>89.74000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>75.16999999999999</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[3, 6, 3, 0, 6]</t>
+          <t>[9, 5, 5, 7, 3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9793251146054944</v>
+        <v>0.9679694352271785</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9793251146054944</v>
+        <v>0.9679694352271785</v>
       </c>
       <c r="E44" t="n">
-        <v>83.67</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>76.75999999999999</v>
+        <v>79.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[8, 2, 6, 3, 7]</t>
+          <t>[6, 3, 7, 9, 3]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9729944194921889</v>
+        <v>0.964912106165948</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9729944194921889</v>
+        <v>0.964912106165948</v>
       </c>
       <c r="E45" t="n">
-        <v>92.35000000000001</v>
+        <v>83.14</v>
       </c>
       <c r="F45" t="n">
-        <v>78.82000000000001</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[3, 3, 1, 8, 3]</t>
+          <t>[4, 4, 6, 3, 2]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9659736259862318</v>
+        <v>0.9579731796438465</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9659736259862318</v>
+        <v>0.9579731796438465</v>
       </c>
       <c r="E46" t="n">
-        <v>89.8</v>
+        <v>94.5</v>
       </c>
       <c r="F46" t="n">
-        <v>69.63000000000001</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[6, 1, 1, 8, 2]</t>
+          <t>[3, 0, 0, 2, 3]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9782390510795363</v>
+        <v>0.9731662871040649</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9782390510795363</v>
+        <v>0.9731662871040649</v>
       </c>
       <c r="E47" t="n">
-        <v>96.03999999999999</v>
+        <v>89.11</v>
       </c>
       <c r="F47" t="n">
-        <v>72.44</v>
+        <v>53.45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[1, 6, 2, 8, 0]</t>
+          <t>[8, 1, 5, 2, 3]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9610856660032717</v>
+        <v>0.9816195107867173</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9610856660032717</v>
+        <v>0.9816195107867173</v>
       </c>
       <c r="E48" t="n">
-        <v>79.27000000000001</v>
+        <v>96.38000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>62.41000000000001</v>
+        <v>78.65000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[6, 6, 4, 1, 1]</t>
+          <t>[0, 1, 0, 2, 3]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9650739201448919</v>
+        <v>0.9741978385226292</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9650739201448919</v>
+        <v>0.9741978385226292</v>
       </c>
       <c r="E49" t="n">
-        <v>96.62</v>
+        <v>96.02</v>
       </c>
       <c r="F49" t="n">
-        <v>74.63999999999999</v>
+        <v>55.43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[5, 0, 8, 2, 1]</t>
+          <t>[3, 7, 9, 5, 5]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9813566976421711</v>
+        <v>0.9473036046156954</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9813566976421711</v>
+        <v>0.9473036046156954</v>
       </c>
       <c r="E50" t="n">
-        <v>93.86</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>70.22</v>
+        <v>65.69999999999999</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[6, 1, 1, 8, 3]</t>
+          <t>[8, 5, 1, 6, 7]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9781502750851661</v>
+        <v>0.9513661609613701</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9781502750851661</v>
+        <v>0.9513661609613701</v>
       </c>
       <c r="E51" t="n">
-        <v>88.15000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="F51" t="n">
-        <v>69.17999999999999</v>
+        <v>71.75</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
@@ -463,7 +463,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[3, 1, 4, 3, 9]</t>
+          <t>[6, 0, 3, 2, 3]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -472,118 +472,118 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9583015808423846</v>
+        <v>0.9557340855135414</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9583015808423846</v>
+        <v>0.9557340855135414</v>
       </c>
       <c r="E2" t="n">
-        <v>78.94</v>
+        <v>90.83</v>
       </c>
       <c r="F2" t="n">
-        <v>75.7</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[6, 9, 8, 3, 9]</t>
+          <t>[3, 2, 4, 8, 8]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9309579595888756</v>
+        <v>0.9713990709281617</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9309579595888756</v>
+        <v>0.9713990709281617</v>
       </c>
       <c r="E3" t="n">
-        <v>92.28</v>
+        <v>115.09</v>
       </c>
       <c r="F3" t="n">
-        <v>72.81999999999999</v>
+        <v>86.59999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[3, 7, 8, 2, 0]</t>
+          <t>[2, 8, 8, 6, 9]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9437457299537613</v>
+        <v>0.9665979929270573</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9437457299537613</v>
+        <v>0.9665979929270573</v>
       </c>
       <c r="E4" t="n">
-        <v>92.13</v>
+        <v>118.5</v>
       </c>
       <c r="F4" t="n">
-        <v>71.51000000000001</v>
+        <v>88.19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[7, 5, 6, 6, 2]</t>
+          <t>[3, 4, 1, 7, 0]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.929686785842423</v>
+        <v>0.9788685992178198</v>
       </c>
       <c r="D5" t="n">
-        <v>0.929686785842423</v>
+        <v>0.9788685992178198</v>
       </c>
       <c r="E5" t="n">
-        <v>94.98999999999999</v>
+        <v>108.33</v>
       </c>
       <c r="F5" t="n">
-        <v>63.77</v>
+        <v>90.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[6, 2, 4, 9, 0]</t>
+          <t>[5, 0, 7, 2, 7]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9444602293351192</v>
+        <v>0.9778656782185453</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9444602293351192</v>
+        <v>0.9778656782185453</v>
       </c>
       <c r="E6" t="n">
-        <v>88.98999999999998</v>
+        <v>104.65</v>
       </c>
       <c r="F6" t="n">
-        <v>74.77</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[3, 6, 1, 3, 9]</t>
+          <t>[3, 3, 9, 6, 2]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -592,262 +592,262 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9536390623316965</v>
+        <v>0.9461228632637724</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9536390623316965</v>
+        <v>0.9461228632637724</v>
       </c>
       <c r="E7" t="n">
-        <v>84.63</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>71.73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[8, 6, 1, 2, 4]</t>
+          <t>[4, 9, 3, 6, 5]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9694718416785735</v>
+        <v>0.9492214640619578</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9694718416785735</v>
+        <v>0.9492214640619578</v>
       </c>
       <c r="E8" t="n">
-        <v>97.87</v>
+        <v>93.39000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>78.33</v>
+        <v>82.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[1, 0, 9, 8, 2]</t>
+          <t>[6, 6, 7, 9, 1]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9544305566812005</v>
+        <v>0.9902853698907322</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9544305566812005</v>
+        <v>0.9902853698907322</v>
       </c>
       <c r="E9" t="n">
-        <v>91.84999999999999</v>
+        <v>113.2</v>
       </c>
       <c r="F9" t="n">
-        <v>69.08</v>
+        <v>96.75999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[2, 8, 7, 6, 5]</t>
+          <t>[3, 9, 7, 2, 6]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.934108671117699</v>
+        <v>0.9694718560354701</v>
       </c>
       <c r="D10" t="n">
-        <v>0.934108671117699</v>
+        <v>0.9694718560354701</v>
       </c>
       <c r="E10" t="n">
-        <v>94.94</v>
+        <v>115.16</v>
       </c>
       <c r="F10" t="n">
-        <v>64.67</v>
+        <v>92.00000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 6, 9]</t>
+          <t>[2, 4, 6, 5, 4]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9790770124522018</v>
+        <v>0.9733818152144124</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9790770124522018</v>
+        <v>0.9733818152144124</v>
       </c>
       <c r="E11" t="n">
-        <v>99.84999999999999</v>
+        <v>117.12</v>
       </c>
       <c r="F11" t="n">
-        <v>70.55000000000001</v>
+        <v>98.34999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[3, 0, 8, 9, 8]</t>
+          <t>[7, 8, 4, 7, 3]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.945697740879988</v>
+        <v>0.9465464755305708</v>
       </c>
       <c r="D12" t="n">
-        <v>0.945697740879988</v>
+        <v>0.9465464755305708</v>
       </c>
       <c r="E12" t="n">
-        <v>95.37</v>
+        <v>94.35000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>74.84</v>
+        <v>73.14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[3, 8, 4, 1, 6]</t>
+          <t>[7, 7, 4, 4, 4]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[3, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9573887977383002</v>
+        <v>0.9947487731100669</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9573887977383002</v>
+        <v>0.9947487731100669</v>
       </c>
       <c r="E13" t="n">
-        <v>98.70999999999999</v>
+        <v>114.28</v>
       </c>
       <c r="F13" t="n">
-        <v>79.67</v>
+        <v>96.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[2, 9, 9, 2, 1]</t>
+          <t>[3, 7, 7, 7, 2]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9447316320263164</v>
+        <v>0.96916419143097</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9447316320263164</v>
+        <v>0.96916419143097</v>
       </c>
       <c r="E14" t="n">
-        <v>84.8</v>
+        <v>97.66</v>
       </c>
       <c r="F14" t="n">
-        <v>70.48</v>
+        <v>85.89999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[5, 3, 5, 9, 2]</t>
+          <t>[9, 6, 3, 3, 1]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.936209006873766</v>
+        <v>0.9697550359017488</v>
       </c>
       <c r="D15" t="n">
-        <v>0.936209006873766</v>
+        <v>0.9697550359017488</v>
       </c>
       <c r="E15" t="n">
-        <v>95.67999999999999</v>
+        <v>113.17</v>
       </c>
       <c r="F15" t="n">
-        <v>78.45</v>
+        <v>94.48999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[8, 6, 4, 2, 8]</t>
+          <t>[5, 9, 3, 8, 2]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.941862794246913</v>
+        <v>0.9679935306627835</v>
       </c>
       <c r="D16" t="n">
-        <v>0.941862794246913</v>
+        <v>0.9679935306627835</v>
       </c>
       <c r="E16" t="n">
-        <v>82.25</v>
+        <v>108.93</v>
       </c>
       <c r="F16" t="n">
-        <v>68.99000000000001</v>
+        <v>86.53999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[9, 8, 0, 4, 1]</t>
+          <t>[1, 9, 1, 4, 9]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.947555151201964</v>
+        <v>0.9676544758794106</v>
       </c>
       <c r="D17" t="n">
-        <v>0.947555151201964</v>
+        <v>0.9676544758794106</v>
       </c>
       <c r="E17" t="n">
-        <v>90.12</v>
+        <v>101.56</v>
       </c>
       <c r="F17" t="n">
-        <v>69.63</v>
+        <v>90.35000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[2, 3, 2, 1, 7]</t>
+          <t>[3, 8, 0, 5, 4]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -856,334 +856,334 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9620498642717544</v>
+        <v>0.9497328879595704</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9620498642717544</v>
+        <v>0.9497328879595704</v>
       </c>
       <c r="E18" t="n">
-        <v>80.55</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>67.06</v>
+        <v>69.33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[5, 2, 2, 2, 8]</t>
+          <t>[2, 2, 7, 4, 7]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9532883383710101</v>
+        <v>0.9757962406026337</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9532883383710101</v>
+        <v>0.9757962406026337</v>
       </c>
       <c r="E19" t="n">
-        <v>84.59999999999999</v>
+        <v>114.99</v>
       </c>
       <c r="F19" t="n">
-        <v>74.13</v>
+        <v>98.36000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[8, 6, 4, 8, 7]</t>
+          <t>[2, 4, 7, 4, 9]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9305792180519352</v>
+        <v>0.9702581915664164</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9305792180519352</v>
+        <v>0.9702581915664164</v>
       </c>
       <c r="E20" t="n">
-        <v>88.63</v>
+        <v>104.05</v>
       </c>
       <c r="F20" t="n">
-        <v>62.95</v>
+        <v>83.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[7, 9, 4, 3, 6]</t>
+          <t>[3, 5, 0, 8, 5]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9381277654907947</v>
+        <v>0.9920718321787946</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9381277654907947</v>
+        <v>0.9920718321787946</v>
       </c>
       <c r="E21" t="n">
-        <v>87.31</v>
+        <v>111.78</v>
       </c>
       <c r="F21" t="n">
-        <v>70.03999999999999</v>
+        <v>96.76999999999998</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[7, 1, 4, 3, 4]</t>
+          <t>[6, 4, 3, 6, 7]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9765113976601729</v>
+        <v>0.9735322849186583</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9765113976601729</v>
+        <v>0.9735322849186583</v>
       </c>
       <c r="E22" t="n">
-        <v>97.91</v>
+        <v>111.87</v>
       </c>
       <c r="F22" t="n">
-        <v>77.5</v>
+        <v>90.42999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[5, 4, 1, 5, 3]</t>
+          <t>[5, 8, 6, 7, 3]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9498755201591262</v>
+        <v>0.9668268802189395</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9498755201591262</v>
+        <v>0.9668268802189395</v>
       </c>
       <c r="E23" t="n">
-        <v>89.42</v>
+        <v>102.29</v>
       </c>
       <c r="F23" t="n">
-        <v>73.15000000000001</v>
+        <v>94.16</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[1, 4, 1, 1, 9]</t>
+          <t>[3, 5, 9, 7, 0]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9832659472797515</v>
+        <v>0.989773756634769</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9832659472797515</v>
+        <v>0.989773756634769</v>
       </c>
       <c r="E24" t="n">
-        <v>95.34</v>
+        <v>113.82</v>
       </c>
       <c r="F24" t="n">
-        <v>68.48</v>
+        <v>96.06999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[8, 6, 1, 3, 1]</t>
+          <t>[7, 0, 3, 7, 8]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 2, 1]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9504670105173136</v>
+        <v>0.9920859062836482</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9504670105173136</v>
+        <v>0.9920859062836482</v>
       </c>
       <c r="E25" t="n">
-        <v>83.22</v>
+        <v>112.11</v>
       </c>
       <c r="F25" t="n">
-        <v>61.12</v>
+        <v>87.74000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[9, 4, 8, 4, 6]</t>
+          <t>[6, 4, 1, 6, 4]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.9350453147580833</v>
+        <v>0.975556451548015</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9350453147580833</v>
+        <v>0.975556451548015</v>
       </c>
       <c r="E26" t="n">
-        <v>82.31999999999999</v>
+        <v>115.24</v>
       </c>
       <c r="F26" t="n">
-        <v>71.87</v>
+        <v>97.83000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[5, 9, 2, 7, 1]</t>
+          <t>[2, 4, 4, 7, 3]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9358313249370387</v>
+        <v>0.9761471480898818</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9358313249370387</v>
+        <v>0.9761471480898818</v>
       </c>
       <c r="E27" t="n">
-        <v>93.96000000000001</v>
+        <v>117.98</v>
       </c>
       <c r="F27" t="n">
-        <v>64.38000000000001</v>
+        <v>92.22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[7, 4, 3, 5, 4]</t>
+          <t>[9, 5, 7, 7, 3]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 3, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9415946870898504</v>
+        <v>0.9936160976734165</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9415946870898504</v>
+        <v>0.9936160976734165</v>
       </c>
       <c r="E28" t="n">
-        <v>84.40000000000001</v>
+        <v>108.96</v>
       </c>
       <c r="F28" t="n">
-        <v>73.95</v>
+        <v>98.91000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[1, 4, 1, 3, 2]</t>
+          <t>[3, 2, 1, 2, 5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9639384292892266</v>
+        <v>0.9751803568794331</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9639384292892266</v>
+        <v>0.9751803568794331</v>
       </c>
       <c r="E29" t="n">
-        <v>73.61999999999999</v>
+        <v>99.05</v>
       </c>
       <c r="F29" t="n">
-        <v>67.61</v>
+        <v>86.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[6, 4, 7, 1, 2]</t>
+          <t>[8, 1, 4, 4, 2]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9459128353270363</v>
+        <v>0.9553075271668551</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9459128353270363</v>
+        <v>0.9553075271668551</v>
       </c>
       <c r="E30" t="n">
-        <v>81.98999999999999</v>
+        <v>111.31</v>
       </c>
       <c r="F30" t="n">
-        <v>61.95000000000001</v>
+        <v>89.55000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[9, 4, 1, 5, 1]</t>
+          <t>[3, 2, 1, 7, 2]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9490747016481383</v>
+        <v>0.9753460538421918</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9490747016481383</v>
+        <v>0.9753460538421918</v>
       </c>
       <c r="E31" t="n">
-        <v>87.03</v>
+        <v>95.91</v>
       </c>
       <c r="F31" t="n">
-        <v>64.92999999999999</v>
+        <v>83.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[8, 1, 3, 2, 6]</t>
+          <t>[1, 5, 6, 3, 1]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1192,166 +1192,166 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9530940688765115</v>
+        <v>0.9532507841901241</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9530940688765115</v>
+        <v>0.9532507841901241</v>
       </c>
       <c r="E32" t="n">
-        <v>82.03999999999999</v>
+        <v>75.02000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>67.16</v>
+        <v>70.52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[1, 6, 1, 6, 6]</t>
+          <t>[3, 3, 6, 2, 0]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9515743153011482</v>
+        <v>0.9717042164212811</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9515743153011482</v>
+        <v>0.9717042164212811</v>
       </c>
       <c r="E33" t="n">
-        <v>86.44</v>
+        <v>110.96</v>
       </c>
       <c r="F33" t="n">
-        <v>54.56</v>
+        <v>86.67000000000002</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[6, 8, 1, 1, 4]</t>
+          <t>[7, 8, 8, 2, 8]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9592775867420309</v>
+        <v>0.9627146935735126</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9592775867420309</v>
+        <v>0.9627146935735126</v>
       </c>
       <c r="E34" t="n">
-        <v>93.41</v>
+        <v>115.99</v>
       </c>
       <c r="F34" t="n">
-        <v>75.36</v>
+        <v>84.71000000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[0, 3, 8, 4, 8]</t>
+          <t>[0, 9, 5, 5, 9]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9525555312480897</v>
+        <v>0.9640256662460518</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9525555312480897</v>
+        <v>0.9640256662460518</v>
       </c>
       <c r="E35" t="n">
-        <v>87.93000000000001</v>
+        <v>97.96999999999998</v>
       </c>
       <c r="F35" t="n">
-        <v>75.58</v>
+        <v>90.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[7, 6, 1, 4, 4]</t>
+          <t>[3, 7, 3, 3, 1]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.970590855374673</v>
+        <v>0.9785481367404134</v>
       </c>
       <c r="D36" t="n">
-        <v>0.970590855374673</v>
+        <v>0.9785481367404134</v>
       </c>
       <c r="E36" t="n">
-        <v>98.66</v>
+        <v>117.8</v>
       </c>
       <c r="F36" t="n">
-        <v>74.46000000000001</v>
+        <v>99.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[4, 1, 6, 1, 1]</t>
+          <t>[3, 5, 8, 9, 1]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9815342890539311</v>
+        <v>0.9453632904858207</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9815342890539311</v>
+        <v>0.9453632904858207</v>
       </c>
       <c r="E37" t="n">
-        <v>96.37</v>
+        <v>98.44999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>67.87</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[1, 4, 1, 4, 8]</t>
+          <t>[8, 8, 4, 2, 5]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9817620991475303</v>
+        <v>0.9445727744832312</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9817620991475303</v>
+        <v>0.9445727744832312</v>
       </c>
       <c r="E38" t="n">
-        <v>87.72</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F38" t="n">
-        <v>79.33</v>
+        <v>72.65000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[2, 7, 4, 2, 5]</t>
+          <t>[9, 7, 9, 4, 4]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,46 +1360,46 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9495966067987122</v>
+        <v>0.9365147498486499</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9495966067987122</v>
+        <v>0.9365147498486499</v>
       </c>
       <c r="E39" t="n">
-        <v>85.34</v>
+        <v>85.62</v>
       </c>
       <c r="F39" t="n">
-        <v>71.16</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[3, 7, 6, 8, 7]</t>
+          <t>[3, 8, 3, 1, 5]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 3, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9311193232190789</v>
+        <v>0.9746138030611522</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9311193232190789</v>
+        <v>0.9746138030611522</v>
       </c>
       <c r="E40" t="n">
-        <v>93.62</v>
+        <v>110.92</v>
       </c>
       <c r="F40" t="n">
-        <v>61.12</v>
+        <v>90.06999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[2, 2, 4, 4, 5]</t>
+          <t>[1, 1, 0, 2, 6]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1408,166 +1408,166 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9559923605265994</v>
+        <v>0.9623801657054274</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9559923605265994</v>
+        <v>0.9623801657054274</v>
       </c>
       <c r="E41" t="n">
-        <v>77.23</v>
+        <v>90.09</v>
       </c>
       <c r="F41" t="n">
-        <v>77.75</v>
+        <v>77.63000000000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[1, 1, 0, 2, 2]</t>
+          <t>[5, 4, 3, 6, 0]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9709232199575138</v>
+        <v>0.9742708716265975</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9709232199575138</v>
+        <v>0.9742708716265975</v>
       </c>
       <c r="E42" t="n">
-        <v>83.41</v>
+        <v>118</v>
       </c>
       <c r="F42" t="n">
-        <v>65.75</v>
+        <v>96.03</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[5, 0, 1, 1, 1]</t>
+          <t>[2, 6, 6, 5, 7]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.966213719926467</v>
+        <v>0.9523010528914727</v>
       </c>
       <c r="D43" t="n">
-        <v>0.966213719926467</v>
+        <v>0.9523010528914727</v>
       </c>
       <c r="E43" t="n">
-        <v>93.08</v>
+        <v>90.36000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>59.46000000000001</v>
+        <v>81.60000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[7, 2, 0, 4, 7]</t>
+          <t>[7, 7, 8, 9, 3]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 2]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9540729274716656</v>
+        <v>0.9638265508712387</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9540729274716656</v>
+        <v>0.9638265508712387</v>
       </c>
       <c r="E44" t="n">
-        <v>92.07999999999998</v>
+        <v>116.92</v>
       </c>
       <c r="F44" t="n">
-        <v>66.3</v>
+        <v>89.59</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[7, 7, 9, 3, 7]</t>
+          <t>[1, 7, 6, 5, 8]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9285708367635412</v>
+        <v>0.9538405794895508</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9285708367635412</v>
+        <v>0.9538405794895508</v>
       </c>
       <c r="E45" t="n">
-        <v>97.84</v>
+        <v>119.12</v>
       </c>
       <c r="F45" t="n">
-        <v>60.83</v>
+        <v>97.25</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[2, 9, 6, 8, 5]</t>
+          <t>[6, 1, 6, 3, 6]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9328522861488242</v>
+        <v>0.9737104026929944</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9328522861488242</v>
+        <v>0.9737104026929944</v>
       </c>
       <c r="E46" t="n">
-        <v>94.27000000000001</v>
+        <v>111.58</v>
       </c>
       <c r="F46" t="n">
-        <v>70.52</v>
+        <v>94.71000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[0, 2, 8, 6, 4]</t>
+          <t>[9, 7, 8, 6, 4]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9513276621804688</v>
+        <v>0.9857968977203522</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9513276621804688</v>
+        <v>0.9857968977203522</v>
       </c>
       <c r="E47" t="n">
-        <v>87.19</v>
+        <v>119.72</v>
       </c>
       <c r="F47" t="n">
-        <v>72.44</v>
+        <v>93.22999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[8, 5, 1, 2, 0]</t>
+          <t>[2, 6, 3, 7, 8]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1576,88 +1576,88 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9524059460663669</v>
+        <v>0.9483210364479586</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9524059460663669</v>
+        <v>0.9483210364479586</v>
       </c>
       <c r="E48" t="n">
-        <v>94.63</v>
+        <v>85.61000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>69.02</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[7, 4, 2, 1, 2]</t>
+          <t>[1, 2, 9, 4, 3]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 3]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.9764374998067096</v>
+        <v>0.956289575580871</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9764374998067096</v>
+        <v>0.956289575580871</v>
       </c>
       <c r="E49" t="n">
-        <v>98.85000000000001</v>
+        <v>118.9</v>
       </c>
       <c r="F49" t="n">
-        <v>74.70999999999999</v>
+        <v>95.45000000000002</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[7, 5, 8, 7, 1]</t>
+          <t>[9, 3, 6, 5, 4]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9258652964458268</v>
+        <v>0.9668604176518857</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9258652964458268</v>
+        <v>0.9668604176518857</v>
       </c>
       <c r="E50" t="n">
-        <v>98.54000000000001</v>
+        <v>114.21</v>
       </c>
       <c r="F50" t="n">
-        <v>56.01000000000001</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[1, 1, 7, 1, 4]</t>
+          <t>[4, 5, 6, 5, 9]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.9635940138353309</v>
+        <v>0.950976574580346</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9635940138353309</v>
+        <v>0.950976574580346</v>
       </c>
       <c r="E51" t="n">
-        <v>80.39000000000001</v>
+        <v>96.91999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>53.29</v>
+        <v>86.56</v>
       </c>
     </row>
   </sheetData>

--- a/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
+++ b/Cenário em Ponte/Cromossomo NT/Geradores/Excel/individuos_2.xlsx
@@ -463,343 +463,343 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[6, 0, 3, 2, 3]</t>
+          <t>[3, 4, 5, 8, 7]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9557340855135414</v>
+        <v>0.9454272199517104</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9557340855135414</v>
+        <v>0.9454272199517104</v>
       </c>
       <c r="E2" t="n">
-        <v>90.83</v>
+        <v>103.51</v>
       </c>
       <c r="F2" t="n">
-        <v>69.73</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[3, 2, 4, 8, 8]</t>
+          <t>[3, 0, 2, 6, 4]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9713990709281617</v>
+        <v>0.9559472769839363</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9713990709281617</v>
+        <v>0.9559472769839363</v>
       </c>
       <c r="E3" t="n">
-        <v>115.09</v>
+        <v>108.92</v>
       </c>
       <c r="F3" t="n">
-        <v>86.59999999999999</v>
+        <v>63.98999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>[2, 8, 8, 6, 9]</t>
+          <t>[2, 0, 5, 1, 4]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9665979929270573</v>
+        <v>0.9587919955179622</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9665979929270573</v>
+        <v>0.9587919955179622</v>
       </c>
       <c r="E4" t="n">
-        <v>118.5</v>
+        <v>99.58000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>88.19</v>
+        <v>64.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[3, 4, 1, 7, 0]</t>
+          <t>[8, 1, 8, 4, 1]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9788685992178198</v>
+        <v>0.9708993411335343</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9788685992178198</v>
+        <v>0.9708993411335343</v>
       </c>
       <c r="E5" t="n">
-        <v>108.33</v>
+        <v>103.69</v>
       </c>
       <c r="F5" t="n">
-        <v>90.69</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>[5, 0, 7, 2, 7]</t>
+          <t>[1, 6, 6, 3, 5]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9778656782185453</v>
+        <v>0.9669321225685688</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9778656782185453</v>
+        <v>0.9669321225685688</v>
       </c>
       <c r="E6" t="n">
-        <v>104.65</v>
+        <v>115.04</v>
       </c>
       <c r="F6" t="n">
-        <v>96.59</v>
+        <v>74.15000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>[3, 3, 9, 6, 2]</t>
+          <t>[9, 0, 6, 3, 6]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9461228632637724</v>
+        <v>0.9740394660799296</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9461228632637724</v>
+        <v>0.9740394660799296</v>
       </c>
       <c r="E7" t="n">
-        <v>87.15000000000001</v>
+        <v>119.28</v>
       </c>
       <c r="F7" t="n">
-        <v>69</v>
+        <v>88.41000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>[4, 9, 3, 6, 5]</t>
+          <t>[5, 3, 5, 2, 9]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9492214640619578</v>
+        <v>0.9440412034407433</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9492214640619578</v>
+        <v>0.9440412034407433</v>
       </c>
       <c r="E8" t="n">
-        <v>93.39000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="F8" t="n">
-        <v>82.62</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>[6, 6, 7, 9, 1]</t>
+          <t>[3, 2, 1, 7, 2]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9902853698907322</v>
+        <v>0.9528299944588935</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9902853698907322</v>
+        <v>0.9528299944588935</v>
       </c>
       <c r="E9" t="n">
-        <v>113.2</v>
+        <v>99.86</v>
       </c>
       <c r="F9" t="n">
-        <v>96.75999999999999</v>
+        <v>60.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>[3, 9, 7, 2, 6]</t>
+          <t>[8, 5, 1, 5, 0]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 3, 1]</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9694718560354701</v>
+        <v>0.9743826903537018</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9694718560354701</v>
+        <v>0.9743826903537018</v>
       </c>
       <c r="E10" t="n">
-        <v>115.16</v>
+        <v>111.87</v>
       </c>
       <c r="F10" t="n">
-        <v>92.00000000000001</v>
+        <v>85.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>[2, 4, 6, 5, 4]</t>
+          <t>[6, 3, 1, 9, 8]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.9733818152144124</v>
+        <v>0.9693056752220642</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9733818152144124</v>
+        <v>0.9693056752220642</v>
       </c>
       <c r="E11" t="n">
-        <v>117.12</v>
+        <v>111.67</v>
       </c>
       <c r="F11" t="n">
-        <v>98.34999999999999</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[7, 8, 4, 7, 3]</t>
+          <t>[1, 7, 7, 5, 3]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.9465464755305708</v>
+        <v>0.9911545506139741</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9465464755305708</v>
+        <v>0.9911545506139741</v>
       </c>
       <c r="E12" t="n">
-        <v>94.35000000000001</v>
+        <v>115.53</v>
       </c>
       <c r="F12" t="n">
-        <v>73.14</v>
+        <v>96.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>[7, 7, 4, 4, 4]</t>
+          <t>[5, 5, 2, 4, 1]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[3, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.9947487731100669</v>
+        <v>0.9459465393475982</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9947487731100669</v>
+        <v>0.9459465393475982</v>
       </c>
       <c r="E13" t="n">
-        <v>114.28</v>
+        <v>94.03999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>96.66</v>
+        <v>58.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>[3, 7, 7, 7, 2]</t>
+          <t>[9, 9, 0, 0, 8]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.96916419143097</v>
+        <v>0.9540474842505979</v>
       </c>
       <c r="D14" t="n">
-        <v>0.96916419143097</v>
+        <v>0.9540474842505979</v>
       </c>
       <c r="E14" t="n">
-        <v>97.66</v>
+        <v>91.94</v>
       </c>
       <c r="F14" t="n">
-        <v>85.89999999999999</v>
+        <v>81.14999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>[9, 6, 3, 3, 1]</t>
+          <t>[5, 5, 4, 6, 7]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 2]</t>
+          <t>[1, 3, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9697550359017488</v>
+        <v>0.9680667419710844</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9697550359017488</v>
+        <v>0.9680667419710844</v>
       </c>
       <c r="E15" t="n">
-        <v>113.17</v>
+        <v>116.84</v>
       </c>
       <c r="F15" t="n">
-        <v>94.48999999999999</v>
+        <v>82.49000000000001</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>[5, 9, 3, 8, 2]</t>
+          <t>[5, 5, 6, 2, 7]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,382 +808,382 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9679935306627835</v>
+        <v>0.9634750889631905</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9679935306627835</v>
+        <v>0.9634750889631905</v>
       </c>
       <c r="E16" t="n">
-        <v>108.93</v>
+        <v>109.09</v>
       </c>
       <c r="F16" t="n">
-        <v>86.53999999999999</v>
+        <v>66.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>[1, 9, 1, 4, 9]</t>
+          <t>[7, 0, 2, 2, 7]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9676544758794106</v>
+        <v>0.9783436266511574</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9676544758794106</v>
+        <v>0.9783436266511574</v>
       </c>
       <c r="E17" t="n">
-        <v>101.56</v>
+        <v>108.18</v>
       </c>
       <c r="F17" t="n">
-        <v>90.35000000000001</v>
+        <v>79.61</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>[3, 8, 0, 5, 4]</t>
+          <t>[5, 2, 4, 7, 5]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.9497328879595704</v>
+        <v>0.9685978498325667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9497328879595704</v>
+        <v>0.9685978498325667</v>
       </c>
       <c r="E18" t="n">
-        <v>89.06999999999999</v>
+        <v>118.97</v>
       </c>
       <c r="F18" t="n">
-        <v>69.33</v>
+        <v>84.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>[2, 2, 7, 4, 7]</t>
+          <t>[4, 3, 4, 3, 1]</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 2]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9757962406026337</v>
+        <v>0.9477443744080057</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9757962406026337</v>
+        <v>0.9477443744080057</v>
       </c>
       <c r="E19" t="n">
-        <v>114.99</v>
+        <v>109.9</v>
       </c>
       <c r="F19" t="n">
-        <v>98.36000000000001</v>
+        <v>66.79000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>[2, 4, 7, 4, 9]</t>
+          <t>[3, 0, 5, 0, 5]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.9702581915664164</v>
+        <v>0.9697287869193245</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9702581915664164</v>
+        <v>0.9697287869193245</v>
       </c>
       <c r="E20" t="n">
-        <v>104.05</v>
+        <v>112.42</v>
       </c>
       <c r="F20" t="n">
-        <v>83.09</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>[3, 5, 0, 8, 5]</t>
+          <t>[2, 6, 7, 1, 9]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[2, 2, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9920718321787946</v>
+        <v>0.9708588786737313</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9920718321787946</v>
+        <v>0.9708588786737313</v>
       </c>
       <c r="E21" t="n">
-        <v>111.78</v>
+        <v>107.56</v>
       </c>
       <c r="F21" t="n">
-        <v>96.76999999999998</v>
+        <v>84.07999999999998</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[6, 4, 3, 6, 7]</t>
+          <t>[6, 7, 8, 8, 1]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9735322849186583</v>
+        <v>0.9639385354386014</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9735322849186583</v>
+        <v>0.9639385354386014</v>
       </c>
       <c r="E22" t="n">
-        <v>111.87</v>
+        <v>114.11</v>
       </c>
       <c r="F22" t="n">
-        <v>90.42999999999999</v>
+        <v>96.76000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>[5, 8, 6, 7, 3]</t>
+          <t>[5, 7, 8, 1, 6]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>[3, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9668268802189395</v>
+        <v>0.9869942511755853</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9668268802189395</v>
+        <v>0.9869942511755853</v>
       </c>
       <c r="E23" t="n">
-        <v>102.29</v>
+        <v>114.41</v>
       </c>
       <c r="F23" t="n">
-        <v>94.16</v>
+        <v>90.68000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>[3, 5, 9, 7, 0]</t>
+          <t>[7, 8, 6, 0, 3]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[3, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.989773756634769</v>
+        <v>0.9755177015151211</v>
       </c>
       <c r="D24" t="n">
-        <v>0.989773756634769</v>
+        <v>0.9755177015151211</v>
       </c>
       <c r="E24" t="n">
-        <v>113.82</v>
+        <v>119.47</v>
       </c>
       <c r="F24" t="n">
-        <v>96.06999999999999</v>
+        <v>98.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>[7, 0, 3, 7, 8]</t>
+          <t>[0, 2, 2, 6, 5]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 2, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.9920859062836482</v>
+        <v>0.9612786909741007</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9920859062836482</v>
+        <v>0.9612786909741007</v>
       </c>
       <c r="E25" t="n">
-        <v>112.11</v>
+        <v>115.21</v>
       </c>
       <c r="F25" t="n">
-        <v>87.74000000000001</v>
+        <v>68.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>[6, 4, 1, 6, 4]</t>
+          <t>[1, 0, 8, 5, 8]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>[2, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 2, 2]</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.975556451548015</v>
+        <v>0.9735186370558575</v>
       </c>
       <c r="D26" t="n">
-        <v>0.975556451548015</v>
+        <v>0.9735186370558575</v>
       </c>
       <c r="E26" t="n">
-        <v>115.24</v>
+        <v>111.57</v>
       </c>
       <c r="F26" t="n">
-        <v>97.83000000000001</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>[2, 4, 4, 7, 3]</t>
+          <t>[1, 0, 7, 5, 7]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[1, 3, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.9761471480898818</v>
+        <v>0.9740230102790015</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9761471480898818</v>
+        <v>0.9740230102790015</v>
       </c>
       <c r="E27" t="n">
-        <v>117.98</v>
+        <v>95.55000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>92.22</v>
+        <v>85.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>[9, 5, 7, 7, 3]</t>
+          <t>[2, 1, 3, 5, 5]</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 3, 1]</t>
+          <t>[1, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.9936160976734165</v>
+        <v>0.9720617129155414</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9936160976734165</v>
+        <v>0.9720617129155414</v>
       </c>
       <c r="E28" t="n">
-        <v>108.96</v>
+        <v>107.17</v>
       </c>
       <c r="F28" t="n">
-        <v>98.91000000000001</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>[3, 2, 1, 2, 5]</t>
+          <t>[8, 8, 4, 1, 5]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>[2, 1, 1, 1, 1]</t>
+          <t>[2, 1, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9751803568794331</v>
+        <v>0.9874941173051041</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9751803568794331</v>
+        <v>0.9874941173051041</v>
       </c>
       <c r="E29" t="n">
-        <v>99.05</v>
+        <v>118.42</v>
       </c>
       <c r="F29" t="n">
-        <v>86.86</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>[8, 1, 4, 4, 2]</t>
+          <t>[5, 5, 5, 2, 9]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9553075271668551</v>
+        <v>0.9745079032027266</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9553075271668551</v>
+        <v>0.9745079032027266</v>
       </c>
       <c r="E30" t="n">
-        <v>111.31</v>
+        <v>114.79</v>
       </c>
       <c r="F30" t="n">
-        <v>89.55000000000001</v>
+        <v>78.83</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>[3, 2, 1, 7, 2]</t>
+          <t>[2, 7, 7, 5, 5]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 2, 1, 2, 1]</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.9753460538421918</v>
+        <v>0.9743070515295524</v>
       </c>
       <c r="D31" t="n">
-        <v>0.9753460538421918</v>
+        <v>0.9743070515295524</v>
       </c>
       <c r="E31" t="n">
-        <v>95.91</v>
+        <v>109.37</v>
       </c>
       <c r="F31" t="n">
-        <v>83.83</v>
+        <v>84.94000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>[1, 5, 6, 3, 1]</t>
+          <t>[5, 0, 4, 3, 7]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1192,214 +1192,214 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9532507841901241</v>
+        <v>0.9513767912540549</v>
       </c>
       <c r="D32" t="n">
-        <v>0.9532507841901241</v>
+        <v>0.9513767912540549</v>
       </c>
       <c r="E32" t="n">
-        <v>75.02000000000001</v>
+        <v>95.05000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>70.52</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>[3, 3, 6, 2, 0]</t>
+          <t>[5, 7, 1, 0, 7]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 2, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.9717042164212811</v>
+        <v>0.9546741208620741</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9717042164212811</v>
+        <v>0.9546741208620741</v>
       </c>
       <c r="E33" t="n">
-        <v>110.96</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>86.67000000000002</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>[7, 8, 8, 2, 8]</t>
+          <t>[5, 5, 6, 1, 2]</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 1]</t>
+          <t>[2, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.9627146935735126</v>
+        <v>0.9903966604187007</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9627146935735126</v>
+        <v>0.9903966604187007</v>
       </c>
       <c r="E34" t="n">
-        <v>115.99</v>
+        <v>119.77</v>
       </c>
       <c r="F34" t="n">
-        <v>84.71000000000001</v>
+        <v>77.84999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>[0, 9, 5, 5, 9]</t>
+          <t>[0, 6, 6, 0, 8]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 1]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9640256662460518</v>
+        <v>0.9621358953375867</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9640256662460518</v>
+        <v>0.9621358953375867</v>
       </c>
       <c r="E35" t="n">
-        <v>97.96999999999998</v>
+        <v>109.74</v>
       </c>
       <c r="F35" t="n">
-        <v>90.58</v>
+        <v>83.66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>[3, 7, 3, 3, 1]</t>
+          <t>[2, 6, 5, 7, 9]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 2]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9785481367404134</v>
+        <v>0.9467417078262782</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9785481367404134</v>
+        <v>0.9467417078262782</v>
       </c>
       <c r="E36" t="n">
-        <v>117.8</v>
+        <v>108.45</v>
       </c>
       <c r="F36" t="n">
-        <v>99.94</v>
+        <v>82.59</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>[3, 5, 8, 9, 1]</t>
+          <t>[8, 1, 4, 7, 8]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.9453632904858207</v>
+        <v>0.9724221398544436</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9453632904858207</v>
+        <v>0.9724221398544436</v>
       </c>
       <c r="E37" t="n">
-        <v>98.44999999999999</v>
+        <v>114.32</v>
       </c>
       <c r="F37" t="n">
-        <v>86.45</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>[8, 8, 4, 2, 5]</t>
+          <t>[8, 7, 0, 8, 7]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9445727744832312</v>
+        <v>0.9625771932539972</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9445727744832312</v>
+        <v>0.9625771932539972</v>
       </c>
       <c r="E38" t="n">
-        <v>91.59999999999999</v>
+        <v>98</v>
       </c>
       <c r="F38" t="n">
-        <v>72.65000000000001</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>[9, 7, 9, 4, 4]</t>
+          <t>[7, 7, 5, 3, 8]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 1]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9365147498486499</v>
+        <v>0.9618356074972312</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9365147498486499</v>
+        <v>0.9618356074972312</v>
       </c>
       <c r="E39" t="n">
-        <v>85.62</v>
+        <v>93.91000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>68.53</v>
+        <v>80.16</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>[3, 8, 3, 1, 5]</t>
+          <t>[3, 9, 9, 0, 1]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>[1, 1, 3, 1, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.9746138030611522</v>
+        <v>0.946371248783749</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9746138030611522</v>
+        <v>0.946371248783749</v>
       </c>
       <c r="E40" t="n">
-        <v>110.92</v>
+        <v>97.34</v>
       </c>
       <c r="F40" t="n">
-        <v>90.06999999999999</v>
+        <v>78.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>[1, 1, 0, 2, 6]</t>
+          <t>[0, 8, 1, 0, 6]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1408,166 +1408,166 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.9623801657054274</v>
+        <v>0.9622994851715773</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9623801657054274</v>
+        <v>0.9622994851715773</v>
       </c>
       <c r="E41" t="n">
-        <v>90.09</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>77.63000000000001</v>
+        <v>72.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>[5, 4, 3, 6, 0]</t>
+          <t>[2, 6, 0, 5, 9]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 3, 1]</t>
+          <t>[1, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9742708716265975</v>
+        <v>0.9507493770366088</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9742708716265975</v>
+        <v>0.9507493770366088</v>
       </c>
       <c r="E42" t="n">
-        <v>118</v>
+        <v>96.16</v>
       </c>
       <c r="F42" t="n">
-        <v>96.03</v>
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>[2, 6, 6, 5, 7]</t>
+          <t>[8, 8, 1, 0, 0]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.9523010528914727</v>
+        <v>0.9717185298960194</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9523010528914727</v>
+        <v>0.9717185298960194</v>
       </c>
       <c r="E43" t="n">
-        <v>90.36000000000001</v>
+        <v>102.38</v>
       </c>
       <c r="F43" t="n">
-        <v>81.60000000000001</v>
+        <v>87.02</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>[7, 7, 8, 9, 3]</t>
+          <t>[8, 1, 9, 9, 6]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>[1, 1, 2, 1, 2]</t>
+          <t>[1, 2, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9638265508712387</v>
+        <v>0.9586687486272211</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9638265508712387</v>
+        <v>0.9586687486272211</v>
       </c>
       <c r="E44" t="n">
-        <v>116.92</v>
+        <v>107.62</v>
       </c>
       <c r="F44" t="n">
-        <v>89.59</v>
+        <v>90.80000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>[1, 7, 6, 5, 8]</t>
+          <t>[5, 1, 4, 0, 0]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[1, 1, 1, 1, 2]</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9538405794895508</v>
+        <v>0.9592066396155352</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9538405794895508</v>
+        <v>0.9592066396155352</v>
       </c>
       <c r="E45" t="n">
-        <v>119.12</v>
+        <v>117.39</v>
       </c>
       <c r="F45" t="n">
-        <v>97.25</v>
+        <v>87.43000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>[6, 1, 6, 3, 6]</t>
+          <t>[4, 5, 9, 5, 9]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 2, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9737104026929944</v>
+        <v>0.9607935199860452</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9737104026929944</v>
+        <v>0.9607935199860452</v>
       </c>
       <c r="E46" t="n">
-        <v>111.58</v>
+        <v>108.44</v>
       </c>
       <c r="F46" t="n">
-        <v>94.71000000000001</v>
+        <v>88.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>[9, 7, 8, 6, 4]</t>
+          <t>[5, 4, 0, 9, 9]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>[1, 2, 2, 1, 1]</t>
+          <t>[1, 1, 2, 1, 1]</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9857968977203522</v>
+        <v>0.9631404501033938</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9857968977203522</v>
+        <v>0.9631404501033938</v>
       </c>
       <c r="E47" t="n">
-        <v>119.72</v>
+        <v>115.84</v>
       </c>
       <c r="F47" t="n">
-        <v>93.22999999999999</v>
+        <v>92.15000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>[2, 6, 3, 7, 8]</t>
+          <t>[4, 3, 0, 5, 1]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9483210364479586</v>
+        <v>0.9530042720451053</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9483210364479586</v>
+        <v>0.9530042720451053</v>
       </c>
       <c r="E48" t="n">
-        <v>85.61000000000001</v>
+        <v>99</v>
       </c>
       <c r="F48" t="n">
-        <v>67.59999999999999</v>
+        <v>67.19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>[1, 2, 9, 4, 3]</t>
+          <t>[1, 5, 4, 0, 7]</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>[1, 1, 1, 1, 3]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.956289575580871</v>
+        <v>0.9745979530227843</v>
       </c>
       <c r="D49" t="n">
-        <v>0.956289575580871</v>
+        <v>0.9745979530227843</v>
       </c>
       <c r="E49" t="n">
-        <v>118.9</v>
+        <v>109.1</v>
       </c>
       <c r="F49" t="n">
-        <v>95.45000000000002</v>
+        <v>84.80000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>[9, 3, 6, 5, 4]</t>
+          <t>[0, 7, 8, 8, 8]</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>[1, 2, 1, 1, 2]</t>
+          <t>[2, 1, 1, 1, 1]</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.9668604176518857</v>
+        <v>0.9625899722199183</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9668604176518857</v>
+        <v>0.9625899722199183</v>
       </c>
       <c r="E50" t="n">
-        <v>114.21</v>
+        <v>98.42999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>92.7</v>
+        <v>87.11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>[4, 5, 6, 5, 9]</t>
+          <t>[0, 8, 4, 8, 7]</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1648,16 +1648,16 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.950976574580346</v>
+        <v>0.9506335078302278</v>
       </c>
       <c r="D51" t="n">
-        <v>0.950976574580346</v>
+        <v>0.9506335078302278</v>
       </c>
       <c r="E51" t="n">
-        <v>96.91999999999999</v>
+        <v>101.48</v>
       </c>
       <c r="F51" t="n">
-        <v>86.56</v>
+        <v>86.53</v>
       </c>
     </row>
   </sheetData>
